--- a/260513_Betonartikel/Results/Members_rc_rib_2.xlsx
+++ b/260513_Betonartikel/Results/Members_rc_rib_2.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,132 +429,132 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Member_1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Member_2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Member_3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Member_4</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Member_5</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Member_6</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Member_7</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Member_8</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Member_9</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Member_10</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Member_11</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Member_12</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Member_13</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Member_14</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Member_15</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Member_16</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Member_17</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Member_18</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Member_19</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Member_20</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Member_21</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Member_22</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Member_23</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Member_24</t>
         </is>
@@ -818,76 +830,76 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1.002080898391656</v>
+        <v>2.499947627467306</v>
       </c>
       <c r="D4" t="n">
-        <v>1.346954242000147</v>
+        <v>2.084005995254688</v>
       </c>
       <c r="E4" t="n">
-        <v>1.722492170110653</v>
+        <v>2.499953143723186</v>
       </c>
       <c r="F4" t="n">
-        <v>1.020645902383281</v>
+        <v>2.0186491503263</v>
       </c>
       <c r="G4" t="n">
-        <v>1.541989224419903</v>
+        <v>2.495778015058522</v>
       </c>
       <c r="H4" t="n">
-        <v>1.319817522981926</v>
+        <v>2.296701739578203</v>
       </c>
       <c r="I4" t="n">
-        <v>1.879700954695243</v>
+        <v>2.499947560636174</v>
       </c>
       <c r="J4" t="n">
-        <v>1.163551886158042</v>
+        <v>2.49994753500091</v>
       </c>
       <c r="K4" t="n">
-        <v>1.911775877760566</v>
+        <v>2.499947541064167</v>
       </c>
       <c r="L4" t="n">
-        <v>1.449402363649418</v>
+        <v>2.056656286456581</v>
       </c>
       <c r="M4" t="n">
-        <v>1.56158784183785</v>
+        <v>2.499947951032927</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000228827912375</v>
+        <v>1.87150225787663</v>
       </c>
       <c r="O4" t="n">
-        <v>1.611202872657195</v>
+        <v>2.499947592820793</v>
       </c>
       <c r="P4" t="n">
-        <v>1.504173377892659</v>
+        <v>2.15552801393065</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.534152456724561</v>
+        <v>2.49994753500091</v>
       </c>
       <c r="R4" t="n">
-        <v>1.020645903047509</v>
+        <v>2.221730531240805</v>
       </c>
       <c r="S4" t="n">
-        <v>1.849048964150836</v>
+        <v>2.499959122027789</v>
       </c>
       <c r="T4" t="n">
-        <v>1.505159097737707</v>
+        <v>2.278182667764771</v>
       </c>
       <c r="U4" t="n">
-        <v>1.640298834155282</v>
+        <v>2.338442072821263</v>
       </c>
       <c r="V4" t="n">
-        <v>1.260938005054399</v>
+        <v>2.465352352356113</v>
       </c>
       <c r="W4" t="n">
-        <v>1.878012233466257</v>
+        <v>2.499999997035178</v>
       </c>
       <c r="X4" t="n">
-        <v>1.109407654669588</v>
+        <v>1.954072239980146</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.233595690697982</v>
+        <v>2.419194803916761</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.200923538943343</v>
+        <v>2.317187951640804</v>
       </c>
     </row>
     <row r="5">
@@ -900,76 +912,76 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.150051858797827</v>
+        <v>0.150036675074003</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1612786835309548</v>
+        <v>0.1545790890685192</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1858177215066689</v>
+        <v>0.1500381538830016</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1500387470905014</v>
+        <v>0.1600065139110834</v>
       </c>
       <c r="G5" t="n">
+        <v>0.1570943284912777</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1500000322977542</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1500000016368014</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.1500366750616904</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.1506643715441982</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.1500363496104777</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.153602288823897</v>
-      </c>
       <c r="K5" t="n">
+        <v>0.1500597022315139</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1617753943780187</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1500366750640512</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1656788666480968</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1500366750908786</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1500624385112598</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1500572761944292</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1526192371710123</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1500358791643298</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1560658752090961</v>
+      </c>
+      <c r="U5" t="n">
         <v>0.1500366750616904</v>
       </c>
-      <c r="L5" t="n">
-        <v>0.1500366750616904</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.1665400266838117</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.1500407106951166</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.1500275866900537</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.16274397849522</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.1500466092950016</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.1500387470915458</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.1500366750619959</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.2051635307632814</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1500621394620596</v>
-      </c>
       <c r="V5" t="n">
-        <v>0.1506530751393457</v>
+        <v>0.1584726956382905</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1500275397512991</v>
+        <v>0.1500366769737873</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1508130800654759</v>
+        <v>0.1500389602352898</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1500572764349752</v>
+        <v>0.1703557925807437</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1500345369256527</v>
+        <v>0.1500759094191566</v>
       </c>
     </row>
     <row r="6">
@@ -982,76 +994,76 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5475429742459657</v>
+        <v>0.2214523305484609</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4464686662545462</v>
+        <v>0.4103306603162796</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3844216092634942</v>
+        <v>0.2493093827162495</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4518111159315371</v>
+        <v>0.4054585382293546</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3947952507293761</v>
+        <v>0.1920840769294572</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4243973821300128</v>
+        <v>0.3903181678576595</v>
       </c>
       <c r="I6" t="n">
-        <v>0.415080120183439</v>
+        <v>0.2359656355964897</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4554088605162943</v>
+        <v>0.3974515568029404</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5063162909776658</v>
+        <v>0.2233097322427277</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5099944568021977</v>
+        <v>0.3893830899694704</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3787243501282133</v>
+        <v>0.2141402115115573</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4352495822316284</v>
+        <v>0.3830684645346287</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4332248151543789</v>
+        <v>0.222619701870471</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4497807596172481</v>
+        <v>0.4199311102146458</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3978455539551671</v>
+        <v>0.2365428291534285</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4518111141249327</v>
+        <v>0.4168743885075791</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4668868418616774</v>
+        <v>0.2292224633358838</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4143107207743069</v>
+        <v>0.3999437277847677</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3975809233577128</v>
+        <v>0.2999855624103779</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4360946629910936</v>
+        <v>0.4060144349064056</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5253307118686699</v>
+        <v>0.2151469009412238</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4282621107435723</v>
+        <v>0.380828154343037</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3909913630580145</v>
+        <v>0.187576856816788</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4440877920762899</v>
+        <v>0.4048293482686973</v>
       </c>
     </row>
     <row r="7">
@@ -1064,76 +1076,76 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1013122997167159</v>
+        <v>0.1064305591907962</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1033005429050846</v>
+        <v>0.1061627153804815</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1046107257155868</v>
+        <v>0.1064316106926892</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1016043316090377</v>
+        <v>0.1059077602504554</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1050138053018947</v>
+        <v>0.1085738241920912</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1040859838687047</v>
+        <v>0.1081583119070432</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1063722216270392</v>
+        <v>0.1085680277599476</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1033048683778992</v>
+        <v>0.1090435102143757</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1061915686290821</v>
+        <v>0.1076876714991077</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1044560565758872</v>
+        <v>0.1067095122731781</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1046939270320125</v>
+        <v>0.107687672785424</v>
       </c>
       <c r="N7" t="n">
-        <v>0.102026620104576</v>
+        <v>0.1059087314771849</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1040849962179216</v>
+        <v>0.1064305590907962</v>
       </c>
       <c r="P7" t="n">
-        <v>0.104099299616256</v>
+        <v>0.1064828514330295</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1036975132518978</v>
+        <v>0.1064330656738096</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1016043315242536</v>
+        <v>0.1067744837324137</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1058606120596501</v>
+        <v>0.1076890591953613</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1047632649406641</v>
+        <v>0.1076806238389508</v>
       </c>
       <c r="U7" t="n">
-        <v>0.104838168873896</v>
+        <v>0.1071745079924843</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1034142129755321</v>
+        <v>0.1085209620180573</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1064914003268523</v>
+        <v>0.1085682015054618</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1035348587983291</v>
+        <v>0.1066591304964343</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1036383599692305</v>
+        <v>0.1083471989424105</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1034846873079912</v>
+        <v>0.1082674727556876</v>
       </c>
     </row>
     <row r="8">
@@ -1146,76 +1158,76 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4619704610541098</v>
+        <v>0.1414523305482913</v>
       </c>
       <c r="D8" t="n">
-        <v>0.347472460250512</v>
+        <v>0.3090717287670186</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2893686572031037</v>
+        <v>0.1692883335844083</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3598988966541314</v>
+        <v>0.3048719468232519</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3147558945491394</v>
+        <v>0.1117368030261057</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3432374799119886</v>
+        <v>0.3052486046415664</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3349625057855165</v>
+        <v>0.1559656354014446</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3753634279566287</v>
+        <v>0.3091932052339867</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4164229084586039</v>
+        <v>0.1433097322426107</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4177569918033117</v>
+        <v>0.299687994322985</v>
       </c>
       <c r="M8" t="n">
-        <v>0.291855271201808</v>
+        <v>0.1341402115114713</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3522117039989272</v>
+        <v>0.2959445668838939</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3408787093156271</v>
+        <v>0.1426197018703862</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3468419766595606</v>
+        <v>0.3170160850720951</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3078695358656487</v>
+        <v>0.1564918817171079</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3598988975337087</v>
+        <v>0.3124973254566665</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3790135435813197</v>
+        <v>0.149197197148129</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3204580883382914</v>
+        <v>0.3064990912234342</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3145855561987433</v>
+        <v>0.2199462062300865</v>
       </c>
       <c r="V8" t="n">
-        <v>0.349033366838111</v>
+        <v>0.3088050056634202</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4426664496868276</v>
+        <v>0.1351469009367189</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3353694541182748</v>
+        <v>0.3006036144597037</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3109913630580142</v>
+        <v>0.1066980282379591</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3640498805339525</v>
+        <v>0.3190915960716474</v>
       </c>
     </row>
     <row r="9">
@@ -1228,76 +1240,76 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="n">
-        <v>9</v>
-      </c>
       <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
         <v>8</v>
       </c>
-      <c r="F9" t="n">
-        <v>9</v>
-      </c>
       <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
         <v>8</v>
       </c>
-      <c r="H9" t="n">
-        <v>9</v>
-      </c>
       <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
         <v>8</v>
       </c>
-      <c r="J9" t="n">
-        <v>9</v>
-      </c>
       <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" t="n">
-        <v>9</v>
-      </c>
       <c r="M9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" t="n">
-        <v>9</v>
-      </c>
       <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
         <v>8</v>
       </c>
-      <c r="P9" t="n">
-        <v>9</v>
-      </c>
       <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
         <v>8</v>
       </c>
-      <c r="R9" t="n">
-        <v>9</v>
-      </c>
       <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
         <v>8</v>
       </c>
-      <c r="T9" t="n">
-        <v>9</v>
-      </c>
       <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" t="n">
         <v>8</v>
       </c>
-      <c r="V9" t="n">
-        <v>9</v>
-      </c>
       <c r="W9" t="n">
+        <v>4</v>
+      </c>
+      <c r="X9" t="n">
         <v>8</v>
       </c>
-      <c r="X9" t="n">
-        <v>9</v>
-      </c>
       <c r="Y9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z9" t="n">
         <v>8</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1310,76 +1322,76 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1.002080898391656</v>
+        <v>1.420018865552664</v>
       </c>
       <c r="D10" t="n">
-        <v>1.346954242000147</v>
+        <v>2.084005995254688</v>
       </c>
       <c r="E10" t="n">
-        <v>1.722492170110653</v>
+        <v>1.420021151851038</v>
       </c>
       <c r="F10" t="n">
-        <v>1.020645902383281</v>
+        <v>2.0186491503263</v>
       </c>
       <c r="G10" t="n">
-        <v>1.541989224419903</v>
+        <v>1.424831065804727</v>
       </c>
       <c r="H10" t="n">
-        <v>1.319817522981926</v>
+        <v>2.179340373753844</v>
       </c>
       <c r="I10" t="n">
-        <v>1.879700954695243</v>
+        <v>1.419989513436676</v>
       </c>
       <c r="J10" t="n">
-        <v>1.163551886158042</v>
+        <v>2.220018847049534</v>
       </c>
       <c r="K10" t="n">
-        <v>1.911775877760566</v>
+        <v>1.420037269998045</v>
       </c>
       <c r="L10" t="n">
-        <v>1.449402363649418</v>
+        <v>2.056656286456581</v>
       </c>
       <c r="M10" t="n">
-        <v>1.56158784183785</v>
+        <v>1.420018930257826</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000228827912375</v>
+        <v>1.87150225787663</v>
       </c>
       <c r="O10" t="n">
-        <v>1.611202872657195</v>
+        <v>1.420018858636862</v>
       </c>
       <c r="P10" t="n">
-        <v>1.504173377892659</v>
+        <v>2.151155553595138</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.534152456724561</v>
+        <v>1.420035327955725</v>
       </c>
       <c r="R10" t="n">
-        <v>1.020645903047509</v>
+        <v>2.166441495984971</v>
       </c>
       <c r="S10" t="n">
-        <v>1.849048964150836</v>
+        <v>1.420020527737022</v>
       </c>
       <c r="T10" t="n">
-        <v>1.505159097737707</v>
+        <v>2.180489233720231</v>
       </c>
       <c r="U10" t="n">
-        <v>1.640298834155282</v>
+        <v>1.387717754613605</v>
       </c>
       <c r="V10" t="n">
-        <v>1.260938005054399</v>
+        <v>2.219848626981856</v>
       </c>
       <c r="W10" t="n">
-        <v>1.878012233466257</v>
+        <v>1.420029340986066</v>
       </c>
       <c r="X10" t="n">
-        <v>1.109407654669588</v>
+        <v>1.954072239980146</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.233595690697982</v>
+        <v>1.420123594847947</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.200923538943343</v>
+        <v>2.183498317863486</v>
       </c>
     </row>
     <row r="11">
@@ -1392,76 +1404,76 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.155070107287785</v>
+        <v>0.2212188475547429</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1893832605715189</v>
+        <v>0.2588002467113823</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2174977902268509</v>
+        <v>0.2254485823861083</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1478086095176774</v>
+        <v>0.2518305346766218</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1706447526336524</v>
+        <v>0.2180821778170182</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1588299203122022</v>
+        <v>0.2411667143786382</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2008537078961178</v>
+        <v>0.223390650903998</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1507936957080573</v>
+        <v>0.2670315689130237</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2343347088748937</v>
+        <v>0.2215008190326301</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1963680698203585</v>
+        <v>0.2329541257976268</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1842592821368873</v>
+        <v>0.2201217874104187</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1359029740001622</v>
+        <v>0.212084331600348</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1999295211187461</v>
+        <v>0.2213939932969607</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2112842200683472</v>
+        <v>0.2694084265223567</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1842317091601945</v>
+        <v>0.223605914234927</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1478086069694343</v>
+        <v>0.2795908111706369</v>
       </c>
       <c r="S11" t="n">
-        <v>0.219347963044219</v>
+        <v>0.2224448268417531</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2070094564228371</v>
+        <v>0.260718000332186</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1833445855981925</v>
+        <v>0.220167395448715</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1623618471289928</v>
+        <v>0.288592656729469</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2216566540249187</v>
+        <v>0.2202769916939274</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1536339246581531</v>
+        <v>0.2018668001077055</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1453541721911251</v>
+        <v>0.2138382690120576</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1507394672228088</v>
+        <v>0.2465584478602316</v>
       </c>
     </row>
     <row r="12">
@@ -1474,76 +1486,76 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1651677404203157</v>
+        <v>0.05742965655181611</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1155547855192007</v>
+        <v>0.08850417544710197</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09504484958339252</v>
+        <v>0.06278376402572554</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1284859734925951</v>
+        <v>0.08956350305505778</v>
       </c>
       <c r="G12" t="n">
-        <v>0.09464830555458506</v>
+        <v>0.05294186582412861</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1096700241326534</v>
+        <v>0.0811873384075659</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09198838247736692</v>
+        <v>0.0601482523012626</v>
       </c>
       <c r="J12" t="n">
-        <v>0.127086580519762</v>
+        <v>0.08217284687168835</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1124441357432422</v>
+        <v>0.05777200240803747</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1275114872002943</v>
+        <v>0.08536652719056718</v>
       </c>
       <c r="M12" t="n">
-        <v>0.09338621149598983</v>
+        <v>0.05611402508098001</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1261426961461495</v>
+        <v>0.08784273336136089</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1015816818548253</v>
+        <v>0.05764321680375407</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1115508402680682</v>
+        <v>0.08859531349414378</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.09486646891342733</v>
+        <v>0.06027466933482192</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1284859734446032</v>
+        <v>0.08849347691816284</v>
       </c>
       <c r="S12" t="n">
-        <v>0.104456826710156</v>
+        <v>0.05887396545118411</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1127189682593913</v>
+        <v>0.08474250656053625</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09268205400251307</v>
+        <v>0.07437583517399433</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1141480507558529</v>
+        <v>0.08613236677609831</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1200312041920144</v>
+        <v>0.05629277526491559</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1169407977316215</v>
+        <v>0.08265568977503292</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1027646416702291</v>
+        <v>0.05325380850661426</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1204759859808787</v>
+        <v>0.08409976860081284</v>
       </c>
     </row>
     <row r="13">
@@ -1556,76 +1568,76 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.004158191133797446</v>
+        <v>0.0003152164113143517</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002639038263321456</v>
+        <v>0.002200407562856338</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00199388895407832</v>
+        <v>0.0004438716160880113</v>
       </c>
       <c r="F13" t="n">
-        <v>0.002397886535938031</v>
+        <v>0.002165557374571803</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001786680081667055</v>
+        <v>0.0002202376394607397</v>
       </c>
       <c r="H13" t="n">
-        <v>0.002136917153441986</v>
+        <v>0.001865844396507543</v>
       </c>
       <c r="I13" t="n">
-        <v>0.002173508986691938</v>
+        <v>0.0003780520361906675</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002573129257303716</v>
+        <v>0.001978085672875422</v>
       </c>
       <c r="K13" t="n">
-        <v>0.003955181507786716</v>
+        <v>0.000322819383593981</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003781056843235027</v>
+        <v>0.00194178108068111</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001713465385504523</v>
+        <v>0.0002867658042363193</v>
       </c>
       <c r="N13" t="n">
-        <v>0.002123629570676905</v>
+        <v>0.001843897197177998</v>
       </c>
       <c r="O13" t="n">
-        <v>0.002386733117397408</v>
+        <v>0.0003199559670532705</v>
       </c>
       <c r="P13" t="n">
-        <v>0.002794727153938535</v>
+        <v>0.002320109426038882</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001827598234963426</v>
+        <v>0.0003808685911540905</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002397886504943955</v>
+        <v>0.0023045865925973</v>
       </c>
       <c r="S13" t="n">
-        <v>0.00308084413716552</v>
+        <v>0.0003478212118092353</v>
       </c>
       <c r="T13" t="n">
-        <v>0.00259165133979672</v>
+        <v>0.002071874580751399</v>
       </c>
       <c r="U13" t="n">
-        <v>0.001852656170459043</v>
+        <v>0.0007647053242353352</v>
       </c>
       <c r="V13" t="n">
-        <v>0.002293532483961125</v>
+        <v>0.002202791194398694</v>
       </c>
       <c r="W13" t="n">
-        <v>0.00438201847375202</v>
+        <v>0.0002905580894654165</v>
       </c>
       <c r="X13" t="n">
-        <v>0.002103793970051636</v>
+        <v>0.001693635827647551</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.001639667425988657</v>
+        <v>0.0002178961756638092</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.002371728387403653</v>
+        <v>0.002083398042306424</v>
       </c>
     </row>
     <row r="14">
@@ -1638,76 +1650,76 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>3.876752682194626</v>
+        <v>5.530471188868573</v>
       </c>
       <c r="D14" t="n">
-        <v>4.734581514287973</v>
+        <v>6.470006167784558</v>
       </c>
       <c r="E14" t="n">
-        <v>5.437444755671272</v>
+        <v>5.636214559652709</v>
       </c>
       <c r="F14" t="n">
-        <v>3.695215237941936</v>
+        <v>6.295763366915544</v>
       </c>
       <c r="G14" t="n">
-        <v>4.266118815841311</v>
+        <v>5.452054445425455</v>
       </c>
       <c r="H14" t="n">
-        <v>3.970748007805056</v>
+        <v>6.029167859465954</v>
       </c>
       <c r="I14" t="n">
-        <v>5.021342697402945</v>
+        <v>5.58476627259995</v>
       </c>
       <c r="J14" t="n">
-        <v>3.769842392701432</v>
+        <v>6.675789222825593</v>
       </c>
       <c r="K14" t="n">
-        <v>5.858367721872342</v>
+        <v>5.537520475815751</v>
       </c>
       <c r="L14" t="n">
-        <v>4.909201745508963</v>
+        <v>5.823853144940669</v>
       </c>
       <c r="M14" t="n">
-        <v>4.606482053422182</v>
+        <v>5.503044685260469</v>
       </c>
       <c r="N14" t="n">
-        <v>3.397574350004056</v>
+        <v>5.302108290008698</v>
       </c>
       <c r="O14" t="n">
-        <v>4.998238027968652</v>
+        <v>5.534849832424019</v>
       </c>
       <c r="P14" t="n">
-        <v>5.28210550170868</v>
+        <v>6.735210663058917</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.605792729004864</v>
+        <v>5.590147855873176</v>
       </c>
       <c r="R14" t="n">
-        <v>3.695215174235857</v>
+        <v>6.989770279265923</v>
       </c>
       <c r="S14" t="n">
-        <v>5.483699076105475</v>
+        <v>5.561120671043827</v>
       </c>
       <c r="T14" t="n">
-        <v>5.175236410570927</v>
+        <v>6.51795000830465</v>
       </c>
       <c r="U14" t="n">
-        <v>4.583614639954813</v>
+        <v>5.504184886217875</v>
       </c>
       <c r="V14" t="n">
-        <v>4.05904617822482</v>
+        <v>7.214816418236726</v>
       </c>
       <c r="W14" t="n">
-        <v>5.541416350622969</v>
+        <v>5.506924792348186</v>
       </c>
       <c r="X14" t="n">
-        <v>3.840848116453826</v>
+        <v>5.046670002692638</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.633854304778129</v>
+        <v>5.34595672530144</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.76848668057022</v>
+        <v>6.16396119650579</v>
       </c>
     </row>
     <row r="15">
@@ -4700,76 +4712,76 @@
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>0.01765898189171851</v>
+        <v>0.01565355512046246</v>
       </c>
       <c r="D49" t="n">
+        <v>0.02316977067920253</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.01189753707696096</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.01886059323986204</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.01697791451935058</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.02332959119471751</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.01224770495900781</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.01934299311896362</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.01555417527998812</v>
+      </c>
+      <c r="L49" t="n">
         <v>0.02320773040047108</v>
       </c>
-      <c r="E49" t="n">
-        <v>0.01876121339937758</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.01791925000100145</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.02142443152044416</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.02321682650266299</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.01755969432661063</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.01781987837756287</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.02006211240030284</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.02164665159936068</v>
-      </c>
       <c r="M49" t="n">
-        <v>0.01824096696516806</v>
+        <v>0.01292891688018686</v>
       </c>
       <c r="N49" t="n">
-        <v>0.0179806668774481</v>
+        <v>0.01866183355889296</v>
       </c>
       <c r="O49" t="n">
-        <v>0.02112629611927822</v>
+        <v>0.0156155953990583</v>
       </c>
       <c r="P49" t="n">
-        <v>0.02369013027957266</v>
+        <v>0.02309852265743358</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.01775845391990578</v>
+        <v>0.0122477573201245</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01791925000040019</v>
+        <v>0.01908281331877856</v>
       </c>
       <c r="S49" t="n">
-        <v>0.02064389211988896</v>
+        <v>0.01528632199855956</v>
       </c>
       <c r="T49" t="n">
-        <v>0.02463146963982839</v>
+        <v>0.02352933031987213</v>
       </c>
       <c r="U49" t="n">
-        <v>0.0176970338006898</v>
+        <v>0.01062525839979811</v>
       </c>
       <c r="V49" t="n">
-        <v>0.01850103359919243</v>
+        <v>0.0195417527999327</v>
       </c>
       <c r="W49" t="n">
-        <v>0.0194422161817776</v>
+        <v>0.01587581817913712</v>
       </c>
       <c r="X49" t="n">
-        <v>0.02268737080010095</v>
+        <v>0.02268695775307801</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.01701587424808412</v>
+        <v>0.01393167635966688</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.01801865025677068</v>
+        <v>0.01869973615206689</v>
       </c>
     </row>
     <row r="50">
@@ -5110,76 +5122,76 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>2690.560662170906</v>
+        <v>5866.543765814818</v>
       </c>
       <c r="D54" t="n">
-        <v>4840.178455976565</v>
+        <v>7834.965266671238</v>
       </c>
       <c r="E54" t="n">
-        <v>5706.369706315196</v>
+        <v>5869.644264881308</v>
       </c>
       <c r="F54" t="n">
-        <v>3161.498876765452</v>
+        <v>7488.803867562757</v>
       </c>
       <c r="G54" t="n">
-        <v>4774.580934917556</v>
+        <v>7787.44504079956</v>
       </c>
       <c r="H54" t="n">
-        <v>4201.880217563115</v>
+        <v>8033.406674436776</v>
       </c>
       <c r="I54" t="n">
-        <v>5831.651032872454</v>
+        <v>7733.171158609165</v>
       </c>
       <c r="J54" t="n">
-        <v>3603.34307820567</v>
+        <v>9412.159223468063</v>
       </c>
       <c r="K54" t="n">
-        <v>6694.444107212009</v>
+        <v>6933.187847238238</v>
       </c>
       <c r="L54" t="n">
-        <v>5343.499583945728</v>
+        <v>7170.033909478952</v>
       </c>
       <c r="M54" t="n">
-        <v>5106.448426438869</v>
+        <v>6933.188984212879</v>
       </c>
       <c r="N54" t="n">
-        <v>2988.642390944883</v>
+        <v>6155.836059603345</v>
       </c>
       <c r="O54" t="n">
-        <v>5038.007742437498</v>
+        <v>5866.543684498575</v>
       </c>
       <c r="P54" t="n">
-        <v>5844.231179474077</v>
+        <v>8371.102715437612</v>
       </c>
       <c r="Q54" t="n">
-        <v>4554.004854142453</v>
+        <v>5874.018061936893</v>
       </c>
       <c r="R54" t="n">
-        <v>3161.498694030086</v>
+        <v>8875.093942840525</v>
       </c>
       <c r="S54" t="n">
-        <v>6187.060528774825</v>
+        <v>6937.600057592282</v>
       </c>
       <c r="T54" t="n">
-        <v>5745.09775193339</v>
+        <v>8620.240836658279</v>
       </c>
       <c r="U54" t="n">
-        <v>4896.128132671002</v>
+        <v>6491.661813754395</v>
       </c>
       <c r="V54" t="n">
-        <v>4141.580330670343</v>
+        <v>10095.26868535445</v>
       </c>
       <c r="W54" t="n">
-        <v>6202.699650423307</v>
+        <v>7733.333325033099</v>
       </c>
       <c r="X54" t="n">
-        <v>4627.012495988633</v>
+        <v>6078.575740504906</v>
       </c>
       <c r="Y54" t="n">
-        <v>3815.922669892456</v>
+        <v>7648.694121937731</v>
       </c>
       <c r="Z54" t="n">
-        <v>3718.37854684931</v>
+        <v>8232.887783377018</v>
       </c>
     </row>
     <row r="55">
@@ -5192,76 +5204,76 @@
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>-2690.560662170906</v>
+        <v>-5866.543765814818</v>
       </c>
       <c r="D55" t="n">
-        <v>-4840.178455976565</v>
+        <v>-7834.965266671238</v>
       </c>
       <c r="E55" t="n">
-        <v>-5706.369706315196</v>
+        <v>-5869.644264881308</v>
       </c>
       <c r="F55" t="n">
-        <v>-3161.498876765452</v>
+        <v>-7488.803867562757</v>
       </c>
       <c r="G55" t="n">
-        <v>-4774.580934917556</v>
+        <v>-7787.44504079956</v>
       </c>
       <c r="H55" t="n">
-        <v>-4201.880217563115</v>
+        <v>-8033.406674436776</v>
       </c>
       <c r="I55" t="n">
-        <v>-5831.651032872454</v>
+        <v>-7733.171158609165</v>
       </c>
       <c r="J55" t="n">
-        <v>-3603.34307820567</v>
+        <v>-9412.159223468063</v>
       </c>
       <c r="K55" t="n">
-        <v>-6694.444107212009</v>
+        <v>-6933.187847238238</v>
       </c>
       <c r="L55" t="n">
-        <v>-5343.499583945728</v>
+        <v>-7170.033909478952</v>
       </c>
       <c r="M55" t="n">
-        <v>-5106.448426438869</v>
+        <v>-6933.188984212879</v>
       </c>
       <c r="N55" t="n">
-        <v>-2988.642390944883</v>
+        <v>-6155.836059603345</v>
       </c>
       <c r="O55" t="n">
-        <v>-5038.007742437498</v>
+        <v>-5866.543684498575</v>
       </c>
       <c r="P55" t="n">
-        <v>-5844.231179474077</v>
+        <v>-8371.102715437612</v>
       </c>
       <c r="Q55" t="n">
-        <v>-4554.004854142453</v>
+        <v>-5874.018061936893</v>
       </c>
       <c r="R55" t="n">
-        <v>-3161.498694030086</v>
+        <v>-8875.093942840525</v>
       </c>
       <c r="S55" t="n">
-        <v>-6187.060528774825</v>
+        <v>-6937.600057592282</v>
       </c>
       <c r="T55" t="n">
-        <v>-5745.09775193339</v>
+        <v>-8620.240836658279</v>
       </c>
       <c r="U55" t="n">
-        <v>-4896.128132671002</v>
+        <v>-6491.661813754395</v>
       </c>
       <c r="V55" t="n">
-        <v>-4141.580330670343</v>
+        <v>-10095.26868535445</v>
       </c>
       <c r="W55" t="n">
-        <v>-6202.699650423307</v>
+        <v>-7733.333325033099</v>
       </c>
       <c r="X55" t="n">
-        <v>-4627.012495988633</v>
+        <v>-6078.575740504906</v>
       </c>
       <c r="Y55" t="n">
-        <v>-3815.922669892456</v>
+        <v>-7648.694121937731</v>
       </c>
       <c r="Z55" t="n">
-        <v>-3718.37854684931</v>
+        <v>-8232.887783377018</v>
       </c>
     </row>
     <row r="56">
@@ -5274,76 +5286,76 @@
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>23924.19718931264</v>
+        <v>4227.928297923976</v>
       </c>
       <c r="D56" t="n">
-        <v>17545.0004285271</v>
+        <v>15041.94609791598</v>
       </c>
       <c r="E56" t="n">
-        <v>15158.63161859137</v>
+        <v>5235.299913487085</v>
       </c>
       <c r="F56" t="n">
-        <v>16315.92996223573</v>
+        <v>15081.6749032769</v>
       </c>
       <c r="G56" t="n">
-        <v>17262.78517949627</v>
+        <v>4590.189773200216</v>
       </c>
       <c r="H56" t="n">
-        <v>19690.24804330405</v>
+        <v>17503.74998021808</v>
       </c>
       <c r="I56" t="n">
-        <v>19508.9360878081</v>
+        <v>6235.736674069238</v>
       </c>
       <c r="J56" t="n">
-        <v>22727.89664551425</v>
+        <v>18194.84878185901</v>
       </c>
       <c r="K56" t="n">
-        <v>26108.65425133944</v>
+        <v>5070.326856496856</v>
       </c>
       <c r="L56" t="n">
-        <v>25702.4457916208</v>
+        <v>16606.43342462403</v>
       </c>
       <c r="M56" t="n">
-        <v>15613.08987178153</v>
+        <v>4718.148984389857</v>
       </c>
       <c r="N56" t="n">
-        <v>17862.54895089294</v>
+        <v>16238.87150219003</v>
       </c>
       <c r="O56" t="n">
-        <v>15832.71996628843</v>
+        <v>4266.687626618634</v>
       </c>
       <c r="P56" t="n">
-        <v>18178.16635055673</v>
+        <v>15405.0385977197</v>
       </c>
       <c r="Q56" t="n">
-        <v>13270.60617522699</v>
+        <v>4753.614614240449</v>
       </c>
       <c r="R56" t="n">
-        <v>16315.92984008757</v>
+        <v>15439.6626745873</v>
       </c>
       <c r="S56" t="n">
-        <v>22101.35590806828</v>
+        <v>5308.73569144185</v>
       </c>
       <c r="T56" t="n">
-        <v>22342.43286589284</v>
+        <v>17090.26979347095</v>
       </c>
       <c r="U56" t="n">
-        <v>15798.37292732606</v>
+        <v>8812.713296393866</v>
       </c>
       <c r="V56" t="n">
-        <v>18522.27739530221</v>
+        <v>17904.27684462621</v>
       </c>
       <c r="W56" t="n">
-        <v>31354.22899161051</v>
+        <v>5304.353638045785</v>
       </c>
       <c r="X56" t="n">
-        <v>19597.12444395203</v>
+        <v>16472.15784091198</v>
       </c>
       <c r="Y56" t="n">
-        <v>16497.55273373698</v>
+        <v>4704.322284034897</v>
       </c>
       <c r="Z56" t="n">
-        <v>21253.89801583053</v>
+        <v>18837.84566719717</v>
       </c>
     </row>
     <row r="57">
@@ -5356,76 +5368,76 @@
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>-23924.19718931264</v>
+        <v>-4227.928297923976</v>
       </c>
       <c r="D57" t="n">
-        <v>-17545.0004285271</v>
+        <v>-15041.94609791598</v>
       </c>
       <c r="E57" t="n">
-        <v>-15158.63161859137</v>
+        <v>-5235.299913487085</v>
       </c>
       <c r="F57" t="n">
-        <v>-16315.92996223573</v>
+        <v>-15081.6749032769</v>
       </c>
       <c r="G57" t="n">
-        <v>-17262.78517949627</v>
+        <v>-4590.189773200216</v>
       </c>
       <c r="H57" t="n">
-        <v>-19690.24804330405</v>
+        <v>-17503.74998021808</v>
       </c>
       <c r="I57" t="n">
-        <v>-19508.9360878081</v>
+        <v>-6235.736674069238</v>
       </c>
       <c r="J57" t="n">
-        <v>-22727.89664551425</v>
+        <v>-18194.84878185901</v>
       </c>
       <c r="K57" t="n">
-        <v>-26108.65425133944</v>
+        <v>-5070.326856496856</v>
       </c>
       <c r="L57" t="n">
-        <v>-25702.4457916208</v>
+        <v>-16606.43342462403</v>
       </c>
       <c r="M57" t="n">
-        <v>-15613.08987178153</v>
+        <v>-4718.148984389857</v>
       </c>
       <c r="N57" t="n">
-        <v>-17862.54895089294</v>
+        <v>-16238.87150219003</v>
       </c>
       <c r="O57" t="n">
-        <v>-15832.71996628843</v>
+        <v>-4266.687626618634</v>
       </c>
       <c r="P57" t="n">
-        <v>-18178.16635055673</v>
+        <v>-15405.0385977197</v>
       </c>
       <c r="Q57" t="n">
-        <v>-13270.60617522699</v>
+        <v>-4753.614614240449</v>
       </c>
       <c r="R57" t="n">
-        <v>-16315.92984008757</v>
+        <v>-15439.6626745873</v>
       </c>
       <c r="S57" t="n">
-        <v>-22101.35590806828</v>
+        <v>-5308.73569144185</v>
       </c>
       <c r="T57" t="n">
-        <v>-22342.43286589284</v>
+        <v>-17090.26979347095</v>
       </c>
       <c r="U57" t="n">
-        <v>-15798.37292732606</v>
+        <v>-8812.713296393866</v>
       </c>
       <c r="V57" t="n">
-        <v>-18522.27739530221</v>
+        <v>-17904.27684462621</v>
       </c>
       <c r="W57" t="n">
-        <v>-31354.22899161051</v>
+        <v>-5304.353638045785</v>
       </c>
       <c r="X57" t="n">
-        <v>-19597.12444395203</v>
+        <v>-16472.15784091198</v>
       </c>
       <c r="Y57" t="n">
-        <v>-16497.55273373698</v>
+        <v>-4704.322284034897</v>
       </c>
       <c r="Z57" t="n">
-        <v>-21253.89801583053</v>
+        <v>-18837.84566719717</v>
       </c>
     </row>
     <row r="58">
@@ -5438,76 +5450,76 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0.06057251319185584</v>
+        <v>0.05500000000016959</v>
       </c>
       <c r="D58" t="n">
-        <v>0.07399620600403414</v>
+        <v>0.07625893154926104</v>
       </c>
       <c r="E58" t="n">
-        <v>0.07005295206039047</v>
+        <v>0.05502104913184123</v>
       </c>
       <c r="F58" t="n">
-        <v>0.06691221927740564</v>
+        <v>0.07558659140610273</v>
       </c>
       <c r="G58" t="n">
-        <v>0.05503935618023666</v>
+        <v>0.0553472739033515</v>
       </c>
       <c r="H58" t="n">
-        <v>0.05615990221802427</v>
+        <v>0.06006956321609302</v>
       </c>
       <c r="I58" t="n">
-        <v>0.05511761439792259</v>
+        <v>0.05500000019504513</v>
       </c>
       <c r="J58" t="n">
-        <v>0.05504543255966549</v>
+        <v>0.06325835156895371</v>
       </c>
       <c r="K58" t="n">
-        <v>0.06489338251906199</v>
+        <v>0.055000000000117</v>
       </c>
       <c r="L58" t="n">
-        <v>0.06723746499888596</v>
+        <v>0.06469509564648533</v>
       </c>
       <c r="M58" t="n">
-        <v>0.06186907892640527</v>
+        <v>0.05500000000008593</v>
       </c>
       <c r="N58" t="n">
-        <v>0.05803787823270113</v>
+        <v>0.06212389765073476</v>
       </c>
       <c r="O58" t="n">
-        <v>0.06734610583875178</v>
+        <v>0.05500000000008486</v>
       </c>
       <c r="P58" t="n">
-        <v>0.07793878295768743</v>
+        <v>0.07791502514255066</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.06497601808951831</v>
+        <v>0.05505094743632057</v>
       </c>
       <c r="R58" t="n">
-        <v>0.06691221659122398</v>
+        <v>0.07937706305091252</v>
       </c>
       <c r="S58" t="n">
-        <v>0.06287329828035773</v>
+        <v>0.05502526618775485</v>
       </c>
       <c r="T58" t="n">
-        <v>0.06885263243601542</v>
+        <v>0.06844463656133347</v>
       </c>
       <c r="U58" t="n">
-        <v>0.05799536715896943</v>
+        <v>0.05503935618029138</v>
       </c>
       <c r="V58" t="n">
-        <v>0.06206129615298259</v>
+        <v>0.07220942924298543</v>
       </c>
       <c r="W58" t="n">
-        <v>0.05766426218184225</v>
+        <v>0.0550000000045049</v>
       </c>
       <c r="X58" t="n">
-        <v>0.06789265662529757</v>
+        <v>0.05522453988333332</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.05500000000000033</v>
+        <v>0.05587882857882898</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.05503791154233736</v>
+        <v>0.06073775219704993</v>
       </c>
     </row>
     <row r="59">
@@ -5520,76 +5532,76 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.06057251319185584</v>
+        <v>0.05500000000016959</v>
       </c>
       <c r="D59" t="n">
-        <v>0.07399620600403414</v>
+        <v>0.07625893154926104</v>
       </c>
       <c r="E59" t="n">
-        <v>0.07005295206039047</v>
+        <v>0.05502104913184123</v>
       </c>
       <c r="F59" t="n">
-        <v>0.06691221927740564</v>
+        <v>0.07558659140610273</v>
       </c>
       <c r="G59" t="n">
-        <v>0.05503935618023666</v>
+        <v>0.0553472739033515</v>
       </c>
       <c r="H59" t="n">
-        <v>0.05615990221802427</v>
+        <v>0.06006956321609302</v>
       </c>
       <c r="I59" t="n">
-        <v>0.05511761439792259</v>
+        <v>0.05500000019504513</v>
       </c>
       <c r="J59" t="n">
-        <v>0.05504543255966549</v>
+        <v>0.06325835156895371</v>
       </c>
       <c r="K59" t="n">
-        <v>0.06489338251906199</v>
+        <v>0.055000000000117</v>
       </c>
       <c r="L59" t="n">
-        <v>0.06723746499888596</v>
+        <v>0.06469509564648533</v>
       </c>
       <c r="M59" t="n">
-        <v>0.06186907892640527</v>
+        <v>0.05500000000008593</v>
       </c>
       <c r="N59" t="n">
-        <v>0.05803787823270113</v>
+        <v>0.06212389765073476</v>
       </c>
       <c r="O59" t="n">
-        <v>0.06734610583875178</v>
+        <v>0.05500000000008486</v>
       </c>
       <c r="P59" t="n">
-        <v>0.07793878295768743</v>
+        <v>0.07791502514255066</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.06497601808951831</v>
+        <v>0.05505094743632057</v>
       </c>
       <c r="R59" t="n">
-        <v>0.06691221659122398</v>
+        <v>0.07937706305091252</v>
       </c>
       <c r="S59" t="n">
-        <v>0.06287329828035773</v>
+        <v>0.05502526618775485</v>
       </c>
       <c r="T59" t="n">
-        <v>0.06885263243601542</v>
+        <v>0.06844463656133347</v>
       </c>
       <c r="U59" t="n">
-        <v>0.05799536715896943</v>
+        <v>0.05503935618029138</v>
       </c>
       <c r="V59" t="n">
-        <v>0.06206129615298259</v>
+        <v>0.07220942924298543</v>
       </c>
       <c r="W59" t="n">
-        <v>0.05766426218184225</v>
+        <v>0.0550000000045049</v>
       </c>
       <c r="X59" t="n">
-        <v>0.06789265662529757</v>
+        <v>0.05522453988333332</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.05500000000000033</v>
+        <v>0.05587882857882898</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.05503791154233736</v>
+        <v>0.06073775219704993</v>
       </c>
     </row>
     <row r="60">
@@ -5602,76 +5614,76 @@
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>0.5187134833001064</v>
+        <v>0.1936255529882297</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4148648010543106</v>
+        <v>0.3787457749766783</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3550410025638054</v>
+        <v>0.223360614177769</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4228514909310364</v>
+        <v>0.3760282416094236</v>
       </c>
       <c r="G60" t="n">
-        <v>0.364083034969154</v>
+        <v>0.1635951196697819</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3927889688786813</v>
+        <v>0.3586533722603007</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3863002730201337</v>
+        <v>0.2098417831169858</v>
       </c>
       <c r="J60" t="n">
-        <v>0.4264989213275128</v>
+        <v>0.3677800602434586</v>
       </c>
       <c r="K60" t="n">
-        <v>0.4762852347775144</v>
+        <v>0.1955326446027336</v>
       </c>
       <c r="L60" t="n">
-        <v>0.4791711310025173</v>
+        <v>0.3577792247692348</v>
       </c>
       <c r="M60" t="n">
-        <v>0.3496038666456293</v>
+        <v>0.1876757530714638</v>
       </c>
       <c r="N60" t="n">
-        <v>0.4062592487929043</v>
+        <v>0.3537375477551822</v>
       </c>
       <c r="O60" t="n">
-        <v>0.4026616670947398</v>
+        <v>0.1948119041709419</v>
       </c>
       <c r="P60" t="n">
-        <v>0.4179356944774617</v>
+        <v>0.388381848885929</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.3689663269952141</v>
+        <v>0.2104189504933663</v>
       </c>
       <c r="R60" t="n">
-        <v>0.4228514891247326</v>
+        <v>0.3873329818481898</v>
       </c>
       <c r="S60" t="n">
-        <v>0.4365648958017329</v>
+        <v>0.2015793023366041</v>
       </c>
       <c r="T60" t="n">
-        <v>0.3819949859543926</v>
+        <v>0.3681790626248316</v>
       </c>
       <c r="U60" t="n">
-        <v>0.3687324064573679</v>
+        <v>0.2746729332104789</v>
       </c>
       <c r="V60" t="n">
-        <v>0.4068441461914974</v>
+        <v>0.3762435585064392</v>
       </c>
       <c r="W60" t="n">
-        <v>0.4956096037777811</v>
+        <v>0.1872089918516552</v>
       </c>
       <c r="X60" t="n">
-        <v>0.3969184253435218</v>
+        <v>0.349484675466498</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.3624834259339724</v>
+        <v>0.1606110186369546</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.4150784669479046</v>
+        <v>0.3754794801926639</v>
       </c>
     </row>
     <row r="61">
@@ -5684,76 +5696,76 @@
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5175429742459656</v>
+        <v>0.1814523305483761</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4164686662545461</v>
+        <v>0.3597011945416491</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3544216092634941</v>
+        <v>0.2092988581503289</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4218111159315371</v>
+        <v>0.3551652425263033</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3647952507293761</v>
+        <v>0.1519104399777815</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3943973821300128</v>
+        <v>0.347783386249613</v>
       </c>
       <c r="I61" t="n">
-        <v>0.385080120183439</v>
+        <v>0.1959656354989671</v>
       </c>
       <c r="J61" t="n">
-        <v>0.4254088605162942</v>
+        <v>0.3533223810184636</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4763162909776658</v>
+        <v>0.1833097322426692</v>
       </c>
       <c r="L61" t="n">
-        <v>0.4799944568021977</v>
+        <v>0.3445355421462277</v>
       </c>
       <c r="M61" t="n">
-        <v>0.3487243501282133</v>
+        <v>0.1741402115115143</v>
       </c>
       <c r="N61" t="n">
-        <v>0.4052495822316283</v>
+        <v>0.3395065157092613</v>
       </c>
       <c r="O61" t="n">
-        <v>0.4032248151543789</v>
+        <v>0.1826197018704286</v>
       </c>
       <c r="P61" t="n">
-        <v>0.419780759617248</v>
+        <v>0.3684735976433705</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.367845553955167</v>
+        <v>0.1965173554352682</v>
       </c>
       <c r="R61" t="n">
-        <v>0.4218111141249327</v>
+        <v>0.3646858569821228</v>
       </c>
       <c r="S61" t="n">
-        <v>0.4368868418616774</v>
+        <v>0.1892098302420064</v>
       </c>
       <c r="T61" t="n">
-        <v>0.3843107207743068</v>
+        <v>0.353221409504101</v>
       </c>
       <c r="U61" t="n">
-        <v>0.3675809233577128</v>
+        <v>0.2599658843202323</v>
       </c>
       <c r="V61" t="n">
-        <v>0.4060946629910936</v>
+        <v>0.3574097202849129</v>
       </c>
       <c r="W61" t="n">
-        <v>0.4953307118686698</v>
+        <v>0.1751469009389713</v>
       </c>
       <c r="X61" t="n">
-        <v>0.3982621107435723</v>
+        <v>0.3407158844013704</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.3609913630580145</v>
+        <v>0.1471374425273735</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.4140877920762899</v>
+        <v>0.3619604721701724</v>
       </c>
     </row>
     <row r="62">
@@ -5766,76 +5778,76 @@
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>11845.98444029941</v>
+        <v>10577.39266457233</v>
       </c>
       <c r="D62" t="n">
-        <v>14901.91014484909</v>
+        <v>15417.02332962987</v>
       </c>
       <c r="E62" t="n">
-        <v>14004.221911473</v>
+        <v>10582.18453395089</v>
       </c>
       <c r="F62" t="n">
-        <v>13289.22893771113</v>
+        <v>15263.96399235018</v>
       </c>
       <c r="G62" t="n">
-        <v>11234.16803740782</v>
+        <v>11304.26601254172</v>
       </c>
       <c r="H62" t="n">
-        <v>11489.26218235875</v>
+        <v>12379.30292652971</v>
       </c>
       <c r="I62" t="n">
-        <v>11251.98364912994</v>
+        <v>11225.20858277359</v>
       </c>
       <c r="J62" t="n">
-        <v>11235.55133515957</v>
+        <v>13105.23582966013</v>
       </c>
       <c r="K62" t="n">
-        <v>13218.326959926</v>
+        <v>10966.08218886287</v>
       </c>
       <c r="L62" t="n">
-        <v>13751.96118442046</v>
+        <v>13173.18662788324</v>
       </c>
       <c r="M62" t="n">
-        <v>12529.83928246836</v>
+        <v>10966.0821888558</v>
       </c>
       <c r="N62" t="n">
-        <v>11657.66015538364</v>
+        <v>12587.84918336333</v>
       </c>
       <c r="O62" t="n">
-        <v>13388.00392565435</v>
+        <v>10577.39266455304</v>
       </c>
       <c r="P62" t="n">
-        <v>15799.44426034253</v>
+        <v>15794.03575472666</v>
       </c>
       <c r="Q62" t="n">
-        <v>12848.44955888949</v>
+        <v>10588.9909320456</v>
       </c>
       <c r="R62" t="n">
-        <v>13289.22832619747</v>
+        <v>16126.87108459473</v>
       </c>
       <c r="S62" t="n">
-        <v>12758.45146688645</v>
+        <v>10971.8340779547</v>
       </c>
       <c r="T62" t="n">
-        <v>14119.65670288447</v>
+        <v>14026.7757722616</v>
       </c>
       <c r="U62" t="n">
-        <v>11647.98243966395</v>
+        <v>10975.04168788528</v>
       </c>
       <c r="V62" t="n">
-        <v>12573.59784963565</v>
+        <v>14883.8370063896</v>
       </c>
       <c r="W62" t="n">
-        <v>11831.73219762579</v>
+        <v>11225.20853939679</v>
       </c>
       <c r="X62" t="n">
-        <v>14160.24298324737</v>
+        <v>11276.32541140877</v>
       </c>
       <c r="Y62" t="n">
-        <v>11225.20853837132</v>
+        <v>11425.27530699544</v>
       </c>
       <c r="Z62" t="n">
-        <v>11233.83916321858</v>
+        <v>12531.41724491985</v>
       </c>
     </row>
     <row r="63">
@@ -5851,13 +5863,13 @@
         <v>0.02008690954980687</v>
       </c>
       <c r="D63" t="n">
+        <v>0.02008690954980687</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.02008690954980687</v>
+      </c>
+      <c r="F63" t="n">
         <v>0.02008690954980686</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0.02008690954980686</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.02008690954980687</v>
       </c>
       <c r="G63" t="n">
         <v>0.01339127303320458</v>
@@ -5866,7 +5878,7 @@
         <v>0.01339127303320458</v>
       </c>
       <c r="I63" t="n">
-        <v>0.01339127303320457</v>
+        <v>0.01339127303320458</v>
       </c>
       <c r="J63" t="n">
         <v>0.01339127303320458</v>
@@ -5890,7 +5902,7 @@
         <v>0.02008690954980687</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.02008690954980686</v>
+        <v>0.02008690954980687</v>
       </c>
       <c r="R63" t="n">
         <v>0.02008690954980686</v>
@@ -6012,13 +6024,13 @@
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -6048,13 +6060,13 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
         <v>1</v>
@@ -6094,76 +6106,76 @@
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>-11845.98444029941</v>
+        <v>-10577.39266457233</v>
       </c>
       <c r="D66" t="n">
-        <v>-14901.91014484909</v>
+        <v>-15417.02332962987</v>
       </c>
       <c r="E66" t="n">
-        <v>-14004.221911473</v>
+        <v>-10582.18453395089</v>
       </c>
       <c r="F66" t="n">
-        <v>-13289.22893771113</v>
+        <v>-15263.96399235018</v>
       </c>
       <c r="G66" t="n">
-        <v>-11234.16803740782</v>
+        <v>-11304.26601254172</v>
       </c>
       <c r="H66" t="n">
-        <v>-11489.26218235875</v>
+        <v>-12379.30292652971</v>
       </c>
       <c r="I66" t="n">
-        <v>-11251.98364912994</v>
+        <v>-11225.20858277359</v>
       </c>
       <c r="J66" t="n">
-        <v>-11235.55133515957</v>
+        <v>-13105.23582966013</v>
       </c>
       <c r="K66" t="n">
-        <v>-13218.326959926</v>
+        <v>-10966.08218886287</v>
       </c>
       <c r="L66" t="n">
-        <v>-13751.96118442046</v>
+        <v>-13173.18662788324</v>
       </c>
       <c r="M66" t="n">
-        <v>-12529.83928246836</v>
+        <v>-10966.0821888558</v>
       </c>
       <c r="N66" t="n">
-        <v>-11657.66015538364</v>
+        <v>-12587.84918336333</v>
       </c>
       <c r="O66" t="n">
-        <v>-13388.00392565435</v>
+        <v>-10577.39266455304</v>
       </c>
       <c r="P66" t="n">
-        <v>-15799.44426034253</v>
+        <v>-15794.03575472666</v>
       </c>
       <c r="Q66" t="n">
-        <v>-12848.44955888949</v>
+        <v>-10588.9909320456</v>
       </c>
       <c r="R66" t="n">
-        <v>-13289.22832619747</v>
+        <v>-16126.87108459473</v>
       </c>
       <c r="S66" t="n">
-        <v>-12758.45146688645</v>
+        <v>-10971.8340779547</v>
       </c>
       <c r="T66" t="n">
-        <v>-14119.65670288447</v>
+        <v>-14026.7757722616</v>
       </c>
       <c r="U66" t="n">
-        <v>-11647.98243966395</v>
+        <v>-10975.04168788528</v>
       </c>
       <c r="V66" t="n">
-        <v>-12573.59784963565</v>
+        <v>-14883.8370063896</v>
       </c>
       <c r="W66" t="n">
-        <v>-11831.73219762579</v>
+        <v>-11225.20853939679</v>
       </c>
       <c r="X66" t="n">
-        <v>-14160.24298324737</v>
+        <v>-11276.32541140877</v>
       </c>
       <c r="Y66" t="n">
-        <v>-11225.20853837132</v>
+        <v>-11425.27530699544</v>
       </c>
       <c r="Z66" t="n">
-        <v>-11233.83916321858</v>
+        <v>-12531.41724491985</v>
       </c>
     </row>
     <row r="67">
@@ -6179,13 +6191,13 @@
         <v>0.02008690954980687</v>
       </c>
       <c r="D67" t="n">
+        <v>0.02008690954980687</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.02008690954980687</v>
+      </c>
+      <c r="F67" t="n">
         <v>0.02008690954980686</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0.02008690954980686</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.02008690954980687</v>
       </c>
       <c r="G67" t="n">
         <v>0.01339127303320458</v>
@@ -6194,7 +6206,7 @@
         <v>0.01339127303320458</v>
       </c>
       <c r="I67" t="n">
-        <v>0.01339127303320457</v>
+        <v>0.01339127303320458</v>
       </c>
       <c r="J67" t="n">
         <v>0.01339127303320458</v>
@@ -6218,7 +6230,7 @@
         <v>0.02008690954980687</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.02008690954980686</v>
+        <v>0.02008690954980687</v>
       </c>
       <c r="R67" t="n">
         <v>0.02008690954980686</v>
@@ -6340,13 +6352,13 @@
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -6376,13 +6388,13 @@
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
         <v>1</v>
@@ -6422,76 +6434,76 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>108774.3003498546</v>
+        <v>31663.10203769293</v>
       </c>
       <c r="D70" t="n">
-        <v>148836.3373030876</v>
+        <v>136443.1469317886</v>
       </c>
       <c r="E70" t="n">
-        <v>125191.0822686894</v>
+        <v>31834.17931244403</v>
       </c>
       <c r="F70" t="n">
-        <v>135119.1827361756</v>
+        <v>134562.6835704026</v>
       </c>
       <c r="G70" t="n">
-        <v>112539.729022157</v>
+        <v>31525.59288752175</v>
       </c>
       <c r="H70" t="n">
-        <v>142029.2768969848</v>
+        <v>131730.6816550886</v>
       </c>
       <c r="I70" t="n">
-        <v>120696.1011409529</v>
+        <v>31830.89939210517</v>
       </c>
       <c r="J70" t="n">
-        <v>136469.1462651178</v>
+        <v>139313.0311876561</v>
       </c>
       <c r="K70" t="n">
-        <v>129736.253306128</v>
+        <v>31730.88639560619</v>
       </c>
       <c r="L70" t="n">
-        <v>151223.3414711306</v>
+        <v>129631.3649073916</v>
       </c>
       <c r="M70" t="n">
-        <v>116934.6940708798</v>
+        <v>31518.2697610243</v>
       </c>
       <c r="N70" t="n">
-        <v>131264.3571643656</v>
+        <v>124163.5923107915</v>
       </c>
       <c r="O70" t="n">
-        <v>120575.4910755347</v>
+        <v>31710.85857830315</v>
       </c>
       <c r="P70" t="n">
-        <v>156527.7885382288</v>
+        <v>139205.8829490232</v>
       </c>
       <c r="Q70" t="n">
-        <v>116649.888621734</v>
+        <v>31712.00051543415</v>
       </c>
       <c r="R70" t="n">
-        <v>135119.1821357881</v>
+        <v>142086.0116617163</v>
       </c>
       <c r="S70" t="n">
-        <v>125690.004270072</v>
+        <v>31631.42581225177</v>
       </c>
       <c r="T70" t="n">
-        <v>154859.5380872074</v>
+        <v>137243.0116455642</v>
       </c>
       <c r="U70" t="n">
-        <v>116420.3105178119</v>
+        <v>31477.97930683822</v>
       </c>
       <c r="V70" t="n">
-        <v>139735.0213558596</v>
+        <v>145122.0483897823</v>
       </c>
       <c r="W70" t="n">
-        <v>127057.8177120094</v>
+        <v>31703.21506173999</v>
       </c>
       <c r="X70" t="n">
-        <v>136743.4432122009</v>
+        <v>121268.4624797902</v>
       </c>
       <c r="Y70" t="n">
-        <v>105734.7078186165</v>
+        <v>31238.91196727551</v>
       </c>
       <c r="Z70" t="n">
-        <v>135753.9400863934</v>
+        <v>133036.3809534329</v>
       </c>
     </row>
     <row r="71">
@@ -6504,76 +6516,76 @@
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>0.01875266163224431</v>
+        <v>0.01039839326176741</v>
       </c>
       <c r="D71" t="n">
-        <v>0.02409610670739432</v>
+        <v>0.01552311538029823</v>
       </c>
       <c r="E71" t="n">
-        <v>0.01847099233312802</v>
+        <v>0.009010418402310939</v>
       </c>
       <c r="F71" t="n">
-        <v>0.02843742041444891</v>
+        <v>0.01592852245931366</v>
       </c>
       <c r="G71" t="n">
-        <v>0.01195860152769478</v>
+        <v>0.008127340017830317</v>
       </c>
       <c r="H71" t="n">
-        <v>0.01640721773103054</v>
+        <v>0.01003303465893487</v>
       </c>
       <c r="I71" t="n">
-        <v>0.009885064782744596</v>
+        <v>0.006365883307012451</v>
       </c>
       <c r="J71" t="n">
-        <v>0.01644591704876009</v>
+        <v>0.01015605564912113</v>
       </c>
       <c r="K71" t="n">
-        <v>0.01014940789444017</v>
+        <v>0.008213317284655478</v>
       </c>
       <c r="L71" t="n">
-        <v>0.01558536059903336</v>
+        <v>0.01262490124730841</v>
       </c>
       <c r="M71" t="n">
-        <v>0.01540795208999174</v>
+        <v>0.008512277585317144</v>
       </c>
       <c r="N71" t="n">
-        <v>0.02337372055572325</v>
+        <v>0.01345655506154601</v>
       </c>
       <c r="O71" t="n">
-        <v>0.0166928648350214</v>
+        <v>0.01034802245238386</v>
       </c>
       <c r="P71" t="n">
-        <v>0.02248388622084572</v>
+        <v>0.01494620623935794</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.01858092897611974</v>
+        <v>0.009548598530711782</v>
       </c>
       <c r="R71" t="n">
-        <v>0.02843742039403372</v>
+        <v>0.01519369750533807</v>
       </c>
       <c r="S71" t="n">
-        <v>0.01111115268935573</v>
+        <v>0.007932968872345835</v>
       </c>
       <c r="T71" t="n">
-        <v>0.01943222844549368</v>
+        <v>0.01224022926381082</v>
       </c>
       <c r="U71" t="n">
-        <v>0.01380681829265309</v>
+        <v>0.005882927296704273</v>
       </c>
       <c r="V71" t="n">
-        <v>0.01962970955583163</v>
+        <v>0.01243996889874736</v>
       </c>
       <c r="W71" t="n">
-        <v>0.008086046571707644</v>
+        <v>0.007130467988586435</v>
       </c>
       <c r="X71" t="n">
-        <v>0.01863890092651967</v>
+        <v>0.01058168987436982</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.01414392907187565</v>
+        <v>0.008235974429414563</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.01629159227779925</v>
+        <v>0.009650559098492956</v>
       </c>
     </row>
     <row r="72">
@@ -6586,76 +6598,76 @@
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0004898365633419052</v>
+        <v>0.0003848981739886571</v>
       </c>
       <c r="D72" t="n">
+        <v>0.0008432635878247042</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.0003335226016572643</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.0008381501630948497</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.0004527813837047168</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.000854937042386396</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.0003534439628030233</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.0008815734266518526</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.0003800264759934331</v>
+      </c>
+      <c r="L72" t="n">
         <v>0.0008460289386518849</v>
       </c>
-      <c r="E72" t="n">
-        <v>0.0008293407073455255</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0.0007565729212373306</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0.0007210053565681168</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.0008466922584734402</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.0007265157592355592</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0.0007482050020458251</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0.0006322272279818382</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0.0007360398558176567</v>
-      </c>
       <c r="M72" t="n">
-        <v>0.0007839833687231931</v>
+        <v>0.000393854147208921</v>
       </c>
       <c r="N72" t="n">
-        <v>0.0007617680020101965</v>
+        <v>0.0008205777928117919</v>
       </c>
       <c r="O72" t="n">
-        <v>0.0007010784256033543</v>
+        <v>0.0003830336886336836</v>
       </c>
       <c r="P72" t="n">
-        <v>0.0008815658844147212</v>
+        <v>0.0008380854194517665</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.0007430558222828684</v>
+        <v>0.0003534469848810702</v>
       </c>
       <c r="R72" t="n">
-        <v>0.000756572921186559</v>
+        <v>0.0008580170926950683</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0006694267133310848</v>
+        <v>0.0003670505541708574</v>
       </c>
       <c r="T72" t="n">
-        <v>0.0009530167345595365</v>
+        <v>0.0008696390048375548</v>
       </c>
       <c r="U72" t="n">
-        <v>0.0007379247839994646</v>
+        <v>0.0002660052066305315</v>
       </c>
       <c r="V72" t="n">
-        <v>0.0008064976751322411</v>
+        <v>0.0008997837934096912</v>
       </c>
       <c r="W72" t="n">
-        <v>0.0005937606503379531</v>
+        <v>0.0003959060239673061</v>
       </c>
       <c r="X72" t="n">
-        <v>0.0008085152490741018</v>
+        <v>0.0008084858096313762</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.0006822124971468051</v>
+        <v>0.0004573175730986409</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.0007649898051431197</v>
+        <v>0.00082391440071786</v>
       </c>
     </row>
     <row r="73">
@@ -6750,76 +6762,76 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>-17387.41820003246</v>
+        <v>-11229.05253937547</v>
       </c>
       <c r="D74" t="n">
-        <v>-14977.35910992125</v>
+        <v>-24114.23654246224</v>
       </c>
       <c r="E74" t="n">
-        <v>-14631.51288741782</v>
+        <v>-13131.43927102115</v>
       </c>
       <c r="F74" t="n">
-        <v>-14116.02722746621</v>
+        <v>-24630.46039142322</v>
       </c>
       <c r="G74" t="n">
-        <v>-12265.58909588409</v>
+        <v>-10051.33422694836</v>
       </c>
       <c r="H74" t="n">
-        <v>-13332.22691716924</v>
+        <v>-22974.66353483399</v>
       </c>
       <c r="I74" t="n">
-        <v>-12958.4129228495</v>
+        <v>-12606.19067242364</v>
       </c>
       <c r="J74" t="n">
-        <v>-14676.60556574137</v>
+        <v>-23358.65676862884</v>
       </c>
       <c r="K74" t="n">
-        <v>-16035.83392675893</v>
+        <v>-11590.98512866291</v>
       </c>
       <c r="L74" t="n">
-        <v>-16161.46570945814</v>
+        <v>-24371.32259720944</v>
       </c>
       <c r="M74" t="n">
-        <v>-12962.29535177205</v>
+        <v>-10962.81640365836</v>
       </c>
       <c r="N74" t="n">
-        <v>-13608.83868089217</v>
+        <v>-24580.01705926358</v>
       </c>
       <c r="O74" t="n">
-        <v>-13480.1802213504</v>
+        <v>-11308.79823307667</v>
       </c>
       <c r="P74" t="n">
-        <v>-15236.14520048992</v>
+        <v>-24009.00699281825</v>
       </c>
       <c r="Q74" t="n">
-        <v>-12273.39199645202</v>
+        <v>-12259.86052951345</v>
       </c>
       <c r="R74" t="n">
-        <v>-14116.02716585707</v>
+        <v>-24154.875353276</v>
       </c>
       <c r="S74" t="n">
-        <v>-14689.07790229131</v>
+        <v>-11992.19145752231</v>
       </c>
       <c r="T74" t="n">
-        <v>-17630.56560005191</v>
+        <v>-24128.38282461068</v>
       </c>
       <c r="U74" t="n">
-        <v>-12323.94962019102</v>
+        <v>-16825.75613524214</v>
       </c>
       <c r="V74" t="n">
-        <v>-13693.36397730219</v>
+        <v>-24802.68626150362</v>
       </c>
       <c r="W74" t="n">
-        <v>-16723.15246843905</v>
+        <v>-11187.09952986664</v>
       </c>
       <c r="X74" t="n">
-        <v>-13478.07320112661</v>
+        <v>-22497.82202095183</v>
       </c>
       <c r="Y74" t="n">
-        <v>-12137.32948055144</v>
+        <v>-10529.62913182174</v>
       </c>
       <c r="Z74" t="n">
-        <v>-13949.03105222063</v>
+        <v>-23955.00625833606</v>
       </c>
     </row>
     <row r="75">
@@ -6832,76 +6844,76 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0.02008690954980687</v>
+        <v>0.04017381909961373</v>
       </c>
       <c r="D75" t="n">
-        <v>0.02008690954980686</v>
+        <v>0.04017381909961373</v>
       </c>
       <c r="E75" t="n">
-        <v>0.02008690954980686</v>
+        <v>0.04017381909961373</v>
       </c>
       <c r="F75" t="n">
-        <v>0.02008690954980686</v>
+        <v>0.04017381909961373</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01339127303320457</v>
+        <v>0.02678254606640915</v>
       </c>
       <c r="H75" t="n">
-        <v>0.01339127303320458</v>
+        <v>0.02678254606640915</v>
       </c>
       <c r="I75" t="n">
-        <v>0.01339127303320458</v>
+        <v>0.02678254606640916</v>
       </c>
       <c r="J75" t="n">
-        <v>0.01339127303320458</v>
+        <v>0.02678254606640915</v>
       </c>
       <c r="K75" t="n">
-        <v>0.01606952763984549</v>
+        <v>0.03213905527969099</v>
       </c>
       <c r="L75" t="n">
-        <v>0.01606952763984549</v>
+        <v>0.03213905527969099</v>
       </c>
       <c r="M75" t="n">
-        <v>0.01606952763984549</v>
+        <v>0.03213905527969099</v>
       </c>
       <c r="N75" t="n">
-        <v>0.01606952763984549</v>
+        <v>0.03213905527969098</v>
       </c>
       <c r="O75" t="n">
-        <v>0.02008690954980687</v>
+        <v>0.04017381909961373</v>
       </c>
       <c r="P75" t="n">
-        <v>0.02008690954980687</v>
+        <v>0.04017381909961373</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.02008690954980687</v>
+        <v>0.04017381909961374</v>
       </c>
       <c r="R75" t="n">
-        <v>0.02008690954980686</v>
+        <v>0.04017381909961373</v>
       </c>
       <c r="S75" t="n">
-        <v>0.01606952763984549</v>
+        <v>0.03213905527969098</v>
       </c>
       <c r="T75" t="n">
-        <v>0.01606952763984549</v>
+        <v>0.03213905527969099</v>
       </c>
       <c r="U75" t="n">
-        <v>0.01606952763984549</v>
+        <v>0.03213905527969098</v>
       </c>
       <c r="V75" t="n">
-        <v>0.01606952763984549</v>
+        <v>0.03213905527969099</v>
       </c>
       <c r="W75" t="n">
-        <v>0.01339127303320458</v>
+        <v>0.02678254606640915</v>
       </c>
       <c r="X75" t="n">
-        <v>0.01339127303320458</v>
+        <v>0.02678254606640915</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.01339127303320458</v>
+        <v>0.02678254606640915</v>
       </c>
       <c r="Z75" t="n">
-        <v>0.01339127303320458</v>
+        <v>0.02678254606640915</v>
       </c>
     </row>
     <row r="76">
@@ -6914,76 +6926,76 @@
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>7.856696954279103e-05</v>
+        <v>0.0001571180387271756</v>
       </c>
       <c r="D76" t="n">
-        <v>8.444532122691349e-05</v>
+        <v>0.0001618748435387541</v>
       </c>
       <c r="E76" t="n">
-        <v>9.729393146535753e-05</v>
+        <v>0.0001571195873323376</v>
       </c>
       <c r="F76" t="n">
-        <v>7.856010426888937e-05</v>
+        <v>0.0001675584295431909</v>
       </c>
       <c r="G76" t="n">
-        <v>7.855901935714091e-05</v>
+        <v>0.0001645087961029399</v>
       </c>
       <c r="H76" t="n">
-        <v>7.888768046682937e-05</v>
+        <v>0.0001570796665016188</v>
       </c>
       <c r="I76" t="n">
-        <v>7.855884895128441e-05</v>
+        <v>0.0001570796343935441</v>
       </c>
       <c r="J76" t="n">
-        <v>8.042597035728875e-05</v>
+        <v>0.0001571180387142818</v>
       </c>
       <c r="K76" t="n">
-        <v>7.855901935714091e-05</v>
+        <v>0.000157142152710132</v>
       </c>
       <c r="L76" t="n">
-        <v>7.855901935714091e-05</v>
+        <v>0.000169410796836525</v>
       </c>
       <c r="M76" t="n">
-        <v>8.720015405975185e-05</v>
+        <v>0.0001571180387167541</v>
       </c>
       <c r="N76" t="n">
-        <v>7.856113240986165e-05</v>
+        <v>0.0001734985034389146</v>
       </c>
       <c r="O76" t="n">
-        <v>7.855426069687978e-05</v>
+        <v>0.0001571180387448476</v>
       </c>
       <c r="P76" t="n">
-        <v>8.521254787609311e-05</v>
+        <v>0.0001571450181355813</v>
       </c>
       <c r="Q76" t="n">
-        <v>7.856422090953917e-05</v>
+        <v>0.0001571396121700378</v>
       </c>
       <c r="R76" t="n">
-        <v>7.85601042694362e-05</v>
+        <v>0.0001598224914309769</v>
       </c>
       <c r="S76" t="n">
-        <v>7.855901935730091e-05</v>
+        <v>0.0001571172052525148</v>
       </c>
       <c r="T76" t="n">
-        <v>0.0001074233735050781</v>
+        <v>0.0001634318023443193</v>
       </c>
       <c r="U76" t="n">
-        <v>7.85723524859956e-05</v>
+        <v>0.0001571180387142818</v>
       </c>
       <c r="V76" t="n">
-        <v>7.888176568307993e-05</v>
+        <v>0.0001659522188039415</v>
       </c>
       <c r="W76" t="n">
-        <v>7.855423611980533e-05</v>
+        <v>0.000157118040716625</v>
       </c>
       <c r="X76" t="n">
-        <v>7.896554406649139e-05</v>
+        <v>0.0001571204317424792</v>
       </c>
       <c r="Y76" t="n">
-        <v>7.856980621096847e-05</v>
+        <v>0.0001783961688227104</v>
       </c>
       <c r="Z76" t="n">
-        <v>7.855789983172951e-05</v>
+        <v>0.0001571591248373433</v>
       </c>
     </row>
     <row r="77">
@@ -7078,76 +7090,76 @@
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>0.008644164621993898</v>
+        <v>0.009519977738121535</v>
       </c>
       <c r="D78" t="n">
-        <v>0.007076021918877209</v>
+        <v>0.006866064931162449</v>
       </c>
       <c r="E78" t="n">
-        <v>0.007474328492922335</v>
+        <v>0.009516335727144234</v>
       </c>
       <c r="F78" t="n">
-        <v>0.007825159309506021</v>
+        <v>0.006927138343693382</v>
       </c>
       <c r="G78" t="n">
-        <v>0.009513170428151028</v>
+        <v>0.009460245079326173</v>
       </c>
       <c r="H78" t="n">
-        <v>0.009323356254531586</v>
+        <v>0.008716540416894916</v>
       </c>
       <c r="I78" t="n">
-        <v>0.009499663244097765</v>
+        <v>0.009519977704390429</v>
       </c>
       <c r="J78" t="n">
-        <v>0.009512120284108106</v>
+        <v>0.008277148591637877</v>
       </c>
       <c r="K78" t="n">
-        <v>0.008068600453127796</v>
+        <v>0.009519977738130637</v>
       </c>
       <c r="L78" t="n">
-        <v>0.007787306907049133</v>
+        <v>0.008093330265085468</v>
       </c>
       <c r="M78" t="n">
-        <v>0.008463012294414986</v>
+        <v>0.009519977738136015</v>
       </c>
       <c r="N78" t="n">
-        <v>0.009021673285486857</v>
+        <v>0.008428298857583127</v>
       </c>
       <c r="O78" t="n">
-        <v>0.007774744643023052</v>
+        <v>0.0095199777381362</v>
       </c>
       <c r="P78" t="n">
-        <v>0.006718077390078801</v>
+        <v>0.00672012586327657</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.008058338922476444</v>
+        <v>0.009511167381886836</v>
       </c>
       <c r="R78" t="n">
-        <v>0.007825159623645956</v>
+        <v>0.006596348560571738</v>
       </c>
       <c r="S78" t="n">
-        <v>0.008327840115266811</v>
+        <v>0.009515606409093918</v>
       </c>
       <c r="T78" t="n">
-        <v>0.007604629729805581</v>
+        <v>0.007649960638319707</v>
       </c>
       <c r="U78" t="n">
-        <v>0.009028286245056047</v>
+        <v>0.009513170428141569</v>
       </c>
       <c r="V78" t="n">
-        <v>0.008436800519080608</v>
+        <v>0.007251113616150931</v>
       </c>
       <c r="W78" t="n">
-        <v>0.009080126161107349</v>
+        <v>0.009519977737371135</v>
       </c>
       <c r="X78" t="n">
-        <v>0.007712156242287919</v>
+        <v>0.009481270042347971</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.009519977738150831</v>
+        <v>0.009370253258971801</v>
       </c>
       <c r="Z78" t="n">
-        <v>0.009513420130331905</v>
+        <v>0.008620647894568123</v>
       </c>
     </row>
     <row r="79">
@@ -7160,76 +7172,76 @@
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>0.008644164621993898</v>
+        <v>0.009519977738121535</v>
       </c>
       <c r="D79" t="n">
-        <v>0.007076021918877209</v>
+        <v>0.006866064931162449</v>
       </c>
       <c r="E79" t="n">
-        <v>0.007474328492922335</v>
+        <v>0.009516335727144234</v>
       </c>
       <c r="F79" t="n">
-        <v>0.007825159309506021</v>
+        <v>0.006927138343693382</v>
       </c>
       <c r="G79" t="n">
-        <v>0.009513170428151028</v>
+        <v>0.009460245079326173</v>
       </c>
       <c r="H79" t="n">
-        <v>0.009323356254531586</v>
+        <v>0.008716540416894916</v>
       </c>
       <c r="I79" t="n">
-        <v>0.009499663244097765</v>
+        <v>0.009519977704390429</v>
       </c>
       <c r="J79" t="n">
-        <v>0.009512120284108106</v>
+        <v>0.008277148591637877</v>
       </c>
       <c r="K79" t="n">
-        <v>0.008068600453127796</v>
+        <v>0.009519977738130637</v>
       </c>
       <c r="L79" t="n">
-        <v>0.007787306907049133</v>
+        <v>0.008093330265085468</v>
       </c>
       <c r="M79" t="n">
-        <v>0.008463012294414986</v>
+        <v>0.009519977738136015</v>
       </c>
       <c r="N79" t="n">
-        <v>0.009021673285486857</v>
+        <v>0.008428298857583127</v>
       </c>
       <c r="O79" t="n">
-        <v>0.007774744643023052</v>
+        <v>0.0095199777381362</v>
       </c>
       <c r="P79" t="n">
-        <v>0.006718077390078801</v>
+        <v>0.00672012586327657</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.008058338922476444</v>
+        <v>0.009511167381886836</v>
       </c>
       <c r="R79" t="n">
-        <v>0.007825159623645956</v>
+        <v>0.006596348560571738</v>
       </c>
       <c r="S79" t="n">
-        <v>0.008327840115266811</v>
+        <v>0.009515606409093918</v>
       </c>
       <c r="T79" t="n">
-        <v>0.007604629729805581</v>
+        <v>0.007649960638319707</v>
       </c>
       <c r="U79" t="n">
-        <v>0.009028286245056047</v>
+        <v>0.009513170428141569</v>
       </c>
       <c r="V79" t="n">
-        <v>0.008436800519080608</v>
+        <v>0.007251113616150931</v>
       </c>
       <c r="W79" t="n">
-        <v>0.009080126161107349</v>
+        <v>0.009519977737371135</v>
       </c>
       <c r="X79" t="n">
-        <v>0.007712156242287919</v>
+        <v>0.009481270042347971</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.009519977738150831</v>
+        <v>0.009370253258971801</v>
       </c>
       <c r="Z79" t="n">
-        <v>0.009513420130331905</v>
+        <v>0.008620647894568123</v>
       </c>
     </row>
     <row r="80">
@@ -7242,76 +7254,76 @@
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0009443297294404547</v>
+        <v>0.001987848029604102</v>
       </c>
       <c r="D80" t="n">
-        <v>0.002039288309111406</v>
+        <v>0.002226463352301763</v>
       </c>
       <c r="E80" t="n">
-        <v>0.002335901209597566</v>
+        <v>0.001493202384337192</v>
       </c>
       <c r="F80" t="n">
-        <v>0.00178921663388606</v>
+        <v>0.002228955355873049</v>
       </c>
       <c r="G80" t="n">
-        <v>0.001980332197102241</v>
+        <v>0.002767694932579038</v>
       </c>
       <c r="H80" t="n">
-        <v>0.002155590725703281</v>
+        <v>0.002383741820126834</v>
       </c>
       <c r="I80" t="n">
-        <v>0.001880702163515411</v>
+        <v>0.001684335491020775</v>
       </c>
       <c r="J80" t="n">
-        <v>0.001754295180201103</v>
+        <v>0.002397012567968691</v>
       </c>
       <c r="K80" t="n">
-        <v>0.001327413032816708</v>
+        <v>0.00194354490916613</v>
       </c>
       <c r="L80" t="n">
-        <v>0.00153606886599725</v>
+        <v>0.002364667594094006</v>
       </c>
       <c r="M80" t="n">
-        <v>0.002242490554367541</v>
+        <v>0.002098588340599053</v>
       </c>
       <c r="N80" t="n">
-        <v>0.0018750785471927</v>
+        <v>0.002319736194303311</v>
       </c>
       <c r="O80" t="n">
-        <v>0.001741110423204009</v>
+        <v>0.001966171883919283</v>
       </c>
       <c r="P80" t="n">
-        <v>0.002109333794800487</v>
+        <v>0.002157890287241305</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.002013885192001563</v>
+        <v>0.001679729815457915</v>
       </c>
       <c r="R80" t="n">
-        <v>0.001789216641409025</v>
+        <v>0.002215192438818332</v>
       </c>
       <c r="S80" t="n">
-        <v>0.001533395652670861</v>
+        <v>0.001820874216331713</v>
       </c>
       <c r="T80" t="n">
-        <v>0.002494840952371347</v>
+        <v>0.002362000160024587</v>
       </c>
       <c r="U80" t="n">
-        <v>0.00200124743872975</v>
+        <v>0.0009684434629992995</v>
       </c>
       <c r="V80" t="n">
-        <v>0.001982325867735678</v>
+        <v>0.002391492885570005</v>
       </c>
       <c r="W80" t="n">
-        <v>0.001198041050480088</v>
+        <v>0.002114781026549317</v>
       </c>
       <c r="X80" t="n">
-        <v>0.00203698089443531</v>
+        <v>0.002313365553302719</v>
       </c>
       <c r="Y80" t="n">
-        <v>0.001882051559706546</v>
+        <v>0.002847361139850325</v>
       </c>
       <c r="Z80" t="n">
-        <v>0.001843000459089418</v>
+        <v>0.002194299406974511</v>
       </c>
     </row>
     <row r="81">
@@ -7324,76 +7336,76 @@
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>54167.26471139582</v>
+        <v>49184.88945343991</v>
       </c>
       <c r="D81" t="n">
-        <v>66168.64213214091</v>
+        <v>68191.51831073836</v>
       </c>
       <c r="E81" t="n">
-        <v>62643.30432119146</v>
+        <v>49203.70978120044</v>
       </c>
       <c r="F81" t="n">
-        <v>59835.37116067589</v>
+        <v>67590.44939951476</v>
       </c>
       <c r="G81" t="n">
-        <v>60282.03855472508</v>
+        <v>60619.22709708713</v>
       </c>
       <c r="H81" t="n">
-        <v>61509.10111120027</v>
+        <v>65790.33695552955</v>
       </c>
       <c r="I81" t="n">
-        <v>60367.73610197438</v>
+        <v>60238.94132146356</v>
       </c>
       <c r="J81" t="n">
-        <v>60288.69256433789</v>
+        <v>69282.10945678114</v>
       </c>
       <c r="K81" t="n">
-        <v>64879.98819703049</v>
+        <v>54990.37814179949</v>
       </c>
       <c r="L81" t="n">
-        <v>67223.08564617678</v>
+        <v>64681.78304582552</v>
       </c>
       <c r="M81" t="n">
-        <v>61856.90385853582</v>
+        <v>54990.37814176842</v>
       </c>
       <c r="N81" t="n">
-        <v>58027.1642131122</v>
+        <v>62111.62209595</v>
       </c>
       <c r="O81" t="n">
-        <v>60223.28539499834</v>
+        <v>49184.88945336416</v>
       </c>
       <c r="P81" t="n">
-        <v>69693.28629749527</v>
+        <v>69672.04719378724</v>
       </c>
       <c r="Q81" t="n">
-        <v>58104.30656865321</v>
+        <v>49230.44227579341</v>
       </c>
       <c r="R81" t="n">
-        <v>59835.36875910453</v>
+        <v>70979.07953379942</v>
       </c>
       <c r="S81" t="n">
-        <v>62860.72480919851</v>
+        <v>55015.63548790159</v>
       </c>
       <c r="T81" t="n">
-        <v>68837.5540262429</v>
+        <v>68429.73630121323</v>
       </c>
       <c r="U81" t="n">
-        <v>57984.66882760703</v>
+        <v>55029.72054808646</v>
       </c>
       <c r="V81" t="n">
-        <v>62049.04532314862</v>
+        <v>72192.84492444644</v>
       </c>
       <c r="W81" t="n">
-        <v>63156.44830506935</v>
+        <v>60238.94111281021</v>
       </c>
       <c r="X81" t="n">
-        <v>74356.61880648055</v>
+        <v>60484.82599632265</v>
       </c>
       <c r="Y81" t="n">
-        <v>60238.94110787743</v>
+        <v>61201.31008279963</v>
       </c>
       <c r="Z81" t="n">
-        <v>60280.45658723744</v>
+        <v>66522.02007679545</v>
       </c>
     </row>
     <row r="82">
@@ -7406,76 +7418,76 @@
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>54167.26471139582</v>
+        <v>49184.88945343991</v>
       </c>
       <c r="D82" t="n">
-        <v>66168.64213214091</v>
+        <v>68191.51831073836</v>
       </c>
       <c r="E82" t="n">
-        <v>62643.30432119146</v>
+        <v>49203.70978120044</v>
       </c>
       <c r="F82" t="n">
-        <v>59835.37116067589</v>
+        <v>67590.44939951476</v>
       </c>
       <c r="G82" t="n">
-        <v>60282.03855472508</v>
+        <v>60619.22709708713</v>
       </c>
       <c r="H82" t="n">
-        <v>61509.10111120027</v>
+        <v>65790.33695552955</v>
       </c>
       <c r="I82" t="n">
-        <v>60367.73610197438</v>
+        <v>60238.94132146356</v>
       </c>
       <c r="J82" t="n">
-        <v>60288.69256433789</v>
+        <v>69282.10945678114</v>
       </c>
       <c r="K82" t="n">
-        <v>64879.98819703049</v>
+        <v>54990.37814179949</v>
       </c>
       <c r="L82" t="n">
-        <v>67223.08564617678</v>
+        <v>64681.78304582552</v>
       </c>
       <c r="M82" t="n">
-        <v>61856.90385853582</v>
+        <v>54990.37814176842</v>
       </c>
       <c r="N82" t="n">
-        <v>58027.1642131122</v>
+        <v>62111.62209595</v>
       </c>
       <c r="O82" t="n">
-        <v>60223.28539499834</v>
+        <v>49184.88945336416</v>
       </c>
       <c r="P82" t="n">
-        <v>69693.28629749527</v>
+        <v>69672.04719378724</v>
       </c>
       <c r="Q82" t="n">
-        <v>58104.30656865321</v>
+        <v>49230.44227579341</v>
       </c>
       <c r="R82" t="n">
-        <v>59835.36875910453</v>
+        <v>70979.07953379942</v>
       </c>
       <c r="S82" t="n">
-        <v>62860.72480919851</v>
+        <v>55015.63548790159</v>
       </c>
       <c r="T82" t="n">
-        <v>68837.5540262429</v>
+        <v>68429.73630121323</v>
       </c>
       <c r="U82" t="n">
-        <v>57984.66882760703</v>
+        <v>55029.72054808646</v>
       </c>
       <c r="V82" t="n">
-        <v>62049.04532314862</v>
+        <v>72192.84492444644</v>
       </c>
       <c r="W82" t="n">
-        <v>63156.44830506935</v>
+        <v>60238.94111281021</v>
       </c>
       <c r="X82" t="n">
-        <v>74356.61880648055</v>
+        <v>60484.82599632265</v>
       </c>
       <c r="Y82" t="n">
-        <v>60238.94110787743</v>
+        <v>61201.31008279963</v>
       </c>
       <c r="Z82" t="n">
-        <v>60280.45658723744</v>
+        <v>66522.02007679545</v>
       </c>
     </row>
     <row r="83">
@@ -7570,76 +7582,76 @@
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>463187.0915547697</v>
+        <v>173077.3459015154</v>
       </c>
       <c r="D84" t="n">
-        <v>370577.2617419861</v>
+        <v>338352.832322708</v>
       </c>
       <c r="E84" t="n">
-        <v>317200.0476428586</v>
+        <v>199637.9469488035</v>
       </c>
       <c r="F84" t="n">
-        <v>377701.774451037</v>
+        <v>335928.0225104935</v>
       </c>
       <c r="G84" t="n">
-        <v>398371.5600791285</v>
+        <v>179116.2534360383</v>
       </c>
       <c r="H84" t="n">
-        <v>429741.7545772871</v>
+        <v>392437.3148481625</v>
       </c>
       <c r="I84" t="n">
-        <v>422651.3292216845</v>
+        <v>229716.8025286152</v>
       </c>
       <c r="J84" t="n">
-        <v>466573.0965455574</v>
+        <v>402412.035431244</v>
       </c>
       <c r="K84" t="n">
-        <v>475564.6480753073</v>
+        <v>195411.0881440396</v>
       </c>
       <c r="L84" t="n">
-        <v>478441.7922071067</v>
+        <v>357372.4577250818</v>
       </c>
       <c r="M84" t="n">
-        <v>349215.4666114199</v>
+        <v>187563.7663129536</v>
       </c>
       <c r="N84" t="n">
-        <v>405734.8578960497</v>
+        <v>353339.9138379656</v>
       </c>
       <c r="O84" t="n">
-        <v>359690.7791714181</v>
+        <v>174137.1406113653</v>
       </c>
       <c r="P84" t="n">
-        <v>373316.6896226389</v>
+        <v>346950.6032602712</v>
       </c>
       <c r="Q84" t="n">
-        <v>329626.5977765766</v>
+        <v>188078.5285326324</v>
       </c>
       <c r="R84" t="n">
-        <v>377701.7728397677</v>
+        <v>346014.7789231058</v>
       </c>
       <c r="S84" t="n">
-        <v>435959.4093517305</v>
+        <v>201450.114085958</v>
       </c>
       <c r="T84" t="n">
-        <v>381531.3283051972</v>
+        <v>367748.3185171111</v>
       </c>
       <c r="U84" t="n">
-        <v>368300.3673881224</v>
+        <v>274433.1261530115</v>
       </c>
       <c r="V84" t="n">
-        <v>406318.2452384771</v>
+        <v>375793.7494579963</v>
       </c>
       <c r="W84" t="n">
-        <v>542058.4554350011</v>
+        <v>204955.1095247649</v>
       </c>
       <c r="X84" t="n">
-        <v>434254.0041334953</v>
+        <v>382416.0994934888</v>
       </c>
       <c r="Y84" t="n">
-        <v>396623.3194852202</v>
+        <v>175850.703521962</v>
       </c>
       <c r="Z84" t="n">
-        <v>454096.0432605061</v>
+        <v>410826.4193401837</v>
       </c>
     </row>
     <row r="85">
@@ -7652,76 +7664,76 @@
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>462143.5993247372</v>
+        <v>162202.2652935006</v>
       </c>
       <c r="D85" t="n">
-        <v>372008.0158970581</v>
+        <v>321358.7883967346</v>
       </c>
       <c r="E85" t="n">
-        <v>316647.2937242857</v>
+        <v>187078.0238678454</v>
       </c>
       <c r="F85" t="n">
-        <v>376773.730237247</v>
+        <v>317310.9205951448</v>
       </c>
       <c r="G85" t="n">
-        <v>399149.9473783778</v>
+        <v>166329.1661367109</v>
       </c>
       <c r="H85" t="n">
-        <v>431499.2788849274</v>
+        <v>380556.5577366658</v>
       </c>
       <c r="I85" t="n">
-        <v>421317.9927992654</v>
+        <v>214535.8494828342</v>
       </c>
       <c r="J85" t="n">
-        <v>465382.2244491906</v>
+        <v>386610.7114628771</v>
       </c>
       <c r="K85" t="n">
-        <v>475595.610371714</v>
+        <v>183202.8938330787</v>
       </c>
       <c r="L85" t="n">
-        <v>479262.6114251988</v>
+        <v>344158.31593637</v>
       </c>
       <c r="M85" t="n">
-        <v>348337.9007918019</v>
+        <v>174043.7915030373</v>
       </c>
       <c r="N85" t="n">
-        <v>404727.79293469</v>
+        <v>339140.2156680364</v>
       </c>
       <c r="O85" t="n">
-        <v>360193.1852164216</v>
+        <v>163245.1856487675</v>
       </c>
       <c r="P85" t="n">
-        <v>374962.5767462854</v>
+        <v>329186.9193565234</v>
       </c>
       <c r="Q85" t="n">
-        <v>328626.4935589688</v>
+        <v>175660.6453177259</v>
       </c>
       <c r="R85" t="n">
-        <v>376773.7286256989</v>
+        <v>325806.9492459454</v>
       </c>
       <c r="S85" t="n">
-        <v>436280.4626670838</v>
+        <v>189096.0057781059</v>
       </c>
       <c r="T85" t="n">
-        <v>383841.4279561492</v>
+        <v>352824.9344648861</v>
       </c>
       <c r="U85" t="n">
-        <v>367151.5768604658</v>
+        <v>259751.0600974072</v>
       </c>
       <c r="V85" t="n">
-        <v>405570.6966219618</v>
+        <v>357003.7925257593</v>
       </c>
       <c r="W85" t="n">
-        <v>541753.9055102105</v>
+        <v>191756.9698349473</v>
       </c>
       <c r="X85" t="n">
-        <v>435722.2211896944</v>
+        <v>372831.4273472849</v>
       </c>
       <c r="Y85" t="n">
-        <v>394992.6019425272</v>
+        <v>161105.5801500064</v>
       </c>
       <c r="Z85" t="n">
-        <v>453013.6703392528</v>
+        <v>396051.7703473069</v>
       </c>
     </row>
     <row r="86">
@@ -7816,76 +7828,76 @@
         <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>3876.752682194626</v>
+        <v>5530.471188868572</v>
       </c>
       <c r="D87" t="n">
-        <v>4734.581514287972</v>
+        <v>6470.006167784558</v>
       </c>
       <c r="E87" t="n">
-        <v>5437.444755671272</v>
+        <v>5636.214559652709</v>
       </c>
       <c r="F87" t="n">
-        <v>3695.215237941936</v>
+        <v>6295.763366915544</v>
       </c>
       <c r="G87" t="n">
-        <v>4266.118815841311</v>
+        <v>5452.054445425456</v>
       </c>
       <c r="H87" t="n">
-        <v>3970.748007805056</v>
+        <v>6029.167859465953</v>
       </c>
       <c r="I87" t="n">
-        <v>5021.342697402944</v>
+        <v>5584.76627259995</v>
       </c>
       <c r="J87" t="n">
-        <v>3769.842392701432</v>
+        <v>6675.789222825592</v>
       </c>
       <c r="K87" t="n">
-        <v>5858.367721872341</v>
+        <v>5537.520475815752</v>
       </c>
       <c r="L87" t="n">
-        <v>4909.201745508964</v>
+        <v>5823.853144940669</v>
       </c>
       <c r="M87" t="n">
-        <v>4606.482053422182</v>
+        <v>5503.044685260468</v>
       </c>
       <c r="N87" t="n">
-        <v>3397.574350004056</v>
+        <v>5302.108290008699</v>
       </c>
       <c r="O87" t="n">
-        <v>4998.238027968651</v>
+        <v>5534.849832424019</v>
       </c>
       <c r="P87" t="n">
-        <v>5282.105501708679</v>
+        <v>6735.210663058917</v>
       </c>
       <c r="Q87" t="n">
-        <v>4605.792729004864</v>
+        <v>5590.147855873176</v>
       </c>
       <c r="R87" t="n">
-        <v>3695.215174235857</v>
+        <v>6989.770279265924</v>
       </c>
       <c r="S87" t="n">
-        <v>5483.699076105475</v>
+        <v>5561.120671043826</v>
       </c>
       <c r="T87" t="n">
-        <v>5175.236410570927</v>
+        <v>6517.950008304651</v>
       </c>
       <c r="U87" t="n">
-        <v>4583.614639954812</v>
+        <v>5504.184886217874</v>
       </c>
       <c r="V87" t="n">
-        <v>4059.04617822482</v>
+        <v>7214.816418236726</v>
       </c>
       <c r="W87" t="n">
-        <v>5541.416350622969</v>
+        <v>5506.924792348185</v>
       </c>
       <c r="X87" t="n">
-        <v>3840.848116453827</v>
+        <v>5046.670002692638</v>
       </c>
       <c r="Y87" t="n">
-        <v>3633.854304778129</v>
+        <v>5345.95672530144</v>
       </c>
       <c r="Z87" t="n">
-        <v>3768.48668057022</v>
+        <v>6163.96119650579</v>
       </c>
     </row>
     <row r="88">
@@ -7898,76 +7910,76 @@
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0001135148087052557</v>
+        <v>0.0002725868820471207</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0001671618804669102</v>
+        <v>0.0002625618876117144</v>
       </c>
       <c r="E88" t="n">
-        <v>0.0002081703108308158</v>
+        <v>0.0002726266083060104</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0001207460476673919</v>
+        <v>0.0002531937738188676</v>
       </c>
       <c r="G88" t="n">
-        <v>0.000221690580713216</v>
+        <v>0.0003595705268583025</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0001912064998276662</v>
+        <v>0.0003417673769832559</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0002703873953528765</v>
+        <v>0.000359319062661131</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0001672898729989945</v>
+        <v>0.0003802390545553242</v>
       </c>
       <c r="K88" t="n">
-        <v>0.0002636327952933635</v>
+        <v>0.0003221481221942226</v>
       </c>
       <c r="L88" t="n">
-        <v>0.0002030952542319607</v>
+        <v>0.0002832273421623128</v>
       </c>
       <c r="M88" t="n">
-        <v>0.000210926247356403</v>
+        <v>0.0003221481750235294</v>
       </c>
       <c r="N88" t="n">
-        <v>0.0001315975342021488</v>
+        <v>0.0002532291378376271</v>
       </c>
       <c r="O88" t="n">
-        <v>0.00019117525081472</v>
+        <v>0.0002725868782692101</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0001916280559161958</v>
+        <v>0.0002745660161364668</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.0001791124286655558</v>
+        <v>0.0002726815829823948</v>
       </c>
       <c r="R88" t="n">
-        <v>0.0001207460455355755</v>
+        <v>0.0002857348805807552</v>
       </c>
       <c r="S88" t="n">
-        <v>0.0002514799976989379</v>
+        <v>0.0003222051177164127</v>
       </c>
       <c r="T88" t="n">
-        <v>0.0002132368212763248</v>
+        <v>0.0003218587382023458</v>
       </c>
       <c r="U88" t="n">
-        <v>0.0002157470167550116</v>
+        <v>0.0003014170870492197</v>
       </c>
       <c r="V88" t="n">
-        <v>0.0001705416947260382</v>
+        <v>0.0003572804859995452</v>
       </c>
       <c r="W88" t="n">
-        <v>0.0002748902518009356</v>
+        <v>0.0003593265989115005</v>
       </c>
       <c r="X88" t="n">
-        <v>0.0001741659271783858</v>
+        <v>0.0002812904921676082</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.0001773054977929817</v>
+        <v>0.000349804447465973</v>
       </c>
       <c r="Z88" t="n">
-        <v>0.000172654133973627</v>
+        <v>0.0003464007368072556</v>
       </c>
     </row>
     <row r="89">
@@ -7980,76 +7992,76 @@
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0.001842630701491806</v>
+        <v>0.002134387528006672</v>
       </c>
       <c r="D89" t="n">
-        <v>0.002311995572009217</v>
+        <v>0.002577459757783485</v>
       </c>
       <c r="E89" t="n">
-        <v>0.002390172811669112</v>
+        <v>0.00208309295679822</v>
       </c>
       <c r="F89" t="n">
-        <v>0.002123822672037602</v>
+        <v>0.002559293691472374</v>
       </c>
       <c r="G89" t="n">
-        <v>0.002290143088548287</v>
+        <v>0.00238362878472086</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0023551904897922</v>
+        <v>0.002742749014051124</v>
       </c>
       <c r="I89" t="n">
-        <v>0.002393046950089194</v>
+        <v>0.002276359273715427</v>
       </c>
       <c r="J89" t="n">
-        <v>0.002210408269597701</v>
+        <v>0.00284636712567338</v>
       </c>
       <c r="K89" t="n">
-        <v>0.002285249389122304</v>
+        <v>0.002228662424288608</v>
       </c>
       <c r="L89" t="n">
-        <v>0.002267986934835317</v>
+        <v>0.002629091971009633</v>
       </c>
       <c r="M89" t="n">
-        <v>0.002340233568692349</v>
+        <v>0.002242466087169332</v>
       </c>
       <c r="N89" t="n">
-        <v>0.002150721754020954</v>
+        <v>0.002547732123122559</v>
       </c>
       <c r="O89" t="n">
-        <v>0.002209180739126272</v>
+        <v>0.00213252303511355</v>
       </c>
       <c r="P89" t="n">
-        <v>0.002397232095319804</v>
+        <v>0.002591560021056879</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.002227042451720117</v>
+        <v>0.002103147314212496</v>
       </c>
       <c r="R89" t="n">
-        <v>0.002123822667723744</v>
+        <v>0.002636506896484154</v>
       </c>
       <c r="S89" t="n">
-        <v>0.002298143279282859</v>
+        <v>0.002215775546052796</v>
       </c>
       <c r="T89" t="n">
-        <v>0.002534111301813862</v>
+        <v>0.002723985834783164</v>
       </c>
       <c r="U89" t="n">
-        <v>0.002295188721192081</v>
+        <v>0.00207315497063985</v>
       </c>
       <c r="V89" t="n">
-        <v>0.002273660381463995</v>
+        <v>0.002827494535409321</v>
       </c>
       <c r="W89" t="n">
-        <v>0.002269292941256227</v>
+        <v>0.00231887481370353</v>
       </c>
       <c r="X89" t="n">
-        <v>0.002283010198693963</v>
+        <v>0.00257538477690567</v>
       </c>
       <c r="Y89" t="n">
-        <v>0.002162590850140335</v>
+        <v>0.002382520188049895</v>
       </c>
       <c r="Z89" t="n">
-        <v>0.002236053524118701</v>
+        <v>0.002721072550366312</v>
       </c>
     </row>
     <row r="90">
@@ -8062,76 +8074,76 @@
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>0.1013122997167159</v>
+        <v>0.1064305591907962</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1033005429050846</v>
+        <v>0.1061627153804815</v>
       </c>
       <c r="E90" t="n">
-        <v>0.1046107257155868</v>
+        <v>0.1064316106926892</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1016043316090377</v>
+        <v>0.1059077602504554</v>
       </c>
       <c r="G90" t="n">
-        <v>0.1050138053018947</v>
+        <v>0.1085738241920912</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1040859838687047</v>
+        <v>0.1081583119070432</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1063722216270392</v>
+        <v>0.1085680277599476</v>
       </c>
       <c r="J90" t="n">
-        <v>0.1033048683778992</v>
+        <v>0.1090435102143757</v>
       </c>
       <c r="K90" t="n">
-        <v>0.1061915686290821</v>
+        <v>0.1076876714991077</v>
       </c>
       <c r="L90" t="n">
-        <v>0.1044560565758872</v>
+        <v>0.1067095122731781</v>
       </c>
       <c r="M90" t="n">
-        <v>0.1046939270320125</v>
+        <v>0.107687672785424</v>
       </c>
       <c r="N90" t="n">
-        <v>0.102026620104576</v>
+        <v>0.1059087314771849</v>
       </c>
       <c r="O90" t="n">
-        <v>0.1040849962179216</v>
+        <v>0.1064305590907962</v>
       </c>
       <c r="P90" t="n">
-        <v>0.104099299616256</v>
+        <v>0.1064828514330295</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.1036975132518978</v>
+        <v>0.1064330656738096</v>
       </c>
       <c r="R90" t="n">
-        <v>0.1016043315242536</v>
+        <v>0.1067744837324137</v>
       </c>
       <c r="S90" t="n">
-        <v>0.1058606120596501</v>
+        <v>0.1076890591953613</v>
       </c>
       <c r="T90" t="n">
-        <v>0.1047632649406641</v>
+        <v>0.1076806238389508</v>
       </c>
       <c r="U90" t="n">
-        <v>0.104838168873896</v>
+        <v>0.1071745079924843</v>
       </c>
       <c r="V90" t="n">
-        <v>0.1034142129755321</v>
+        <v>0.1085209620180573</v>
       </c>
       <c r="W90" t="n">
-        <v>0.1064914003268523</v>
+        <v>0.1085682015054618</v>
       </c>
       <c r="X90" t="n">
-        <v>0.1035348587983291</v>
+        <v>0.1066591304964343</v>
       </c>
       <c r="Y90" t="n">
-        <v>0.1036383599692305</v>
+        <v>0.1083471989424105</v>
       </c>
       <c r="Z90" t="n">
-        <v>0.1034846873079912</v>
+        <v>0.1082674727556876</v>
       </c>
     </row>
     <row r="91">
@@ -8226,76 +8238,76 @@
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>10.49559263268339</v>
+        <v>4.873195232801051</v>
       </c>
       <c r="D92" t="n">
-        <v>9.797281855633859</v>
+        <v>7.059344496727733</v>
       </c>
       <c r="E92" t="n">
-        <v>5.245414866060682</v>
+        <v>3.14981160600204</v>
       </c>
       <c r="F92" t="n">
-        <v>7.865945870770878</v>
+        <v>4.792554718216071</v>
       </c>
       <c r="G92" t="n">
-        <v>8.47720578592908</v>
+        <v>5.451350587468005</v>
       </c>
       <c r="H92" t="n">
-        <v>10.18552913998445</v>
+        <v>6.816366211317951</v>
       </c>
       <c r="I92" t="n">
-        <v>4.81249459207788</v>
+        <v>3.442054205616954</v>
       </c>
       <c r="J92" t="n">
-        <v>7.181158945920733</v>
+        <v>4.303955948099542</v>
       </c>
       <c r="K92" t="n">
-        <v>6.822885305551618</v>
+        <v>5.088442157023174</v>
       </c>
       <c r="L92" t="n">
-        <v>8.931471770361126</v>
+        <v>7.296515480555347</v>
       </c>
       <c r="M92" t="n">
-        <v>5.665008721742956</v>
+        <v>3.390804215334002</v>
       </c>
       <c r="N92" t="n">
-        <v>8.128167745039704</v>
+        <v>5.146016859499272</v>
       </c>
       <c r="O92" t="n">
-        <v>7.826227484141555</v>
+        <v>4.868938323624671</v>
       </c>
       <c r="P92" t="n">
-        <v>9.096694974505501</v>
+        <v>6.862447688519771</v>
       </c>
       <c r="Q92" t="n">
-        <v>5.487414581251402</v>
+        <v>3.180142614453854</v>
       </c>
       <c r="R92" t="n">
-        <v>7.865945849674671</v>
+        <v>4.485855973885498</v>
       </c>
       <c r="S92" t="n">
-        <v>7.094146235136802</v>
+        <v>5.058995631583746</v>
       </c>
       <c r="T92" t="n">
-        <v>9.609808305648453</v>
+        <v>6.824765728749782</v>
       </c>
       <c r="U92" t="n">
-        <v>5.289361162444296</v>
+        <v>3.351297235967815</v>
       </c>
       <c r="V92" t="n">
-        <v>6.816158123519028</v>
+        <v>4.335413976006966</v>
       </c>
       <c r="W92" t="n">
-        <v>6.897053455668335</v>
+        <v>5.294302380412825</v>
       </c>
       <c r="X92" t="n">
-        <v>11.74594979443174</v>
+        <v>7.522686369273341</v>
       </c>
       <c r="Y92" t="n">
-        <v>6.62688317924894</v>
+        <v>3.722832918770385</v>
       </c>
       <c r="Z92" t="n">
-        <v>7.03841118536037</v>
+        <v>4.439015452002078</v>
       </c>
     </row>
     <row r="93">
@@ -8308,76 +8320,76 @@
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>28.67753899324554</v>
+        <v>16.44135677500546</v>
       </c>
       <c r="D93" t="n">
-        <v>26.04596736644153</v>
+        <v>23.06508644036499</v>
       </c>
       <c r="E93" t="n">
-        <v>23.42427661232933</v>
+        <v>16.76364127008539</v>
       </c>
       <c r="F93" t="n">
-        <v>26.75965381265617</v>
+        <v>23.16509492035933</v>
       </c>
       <c r="G93" t="n">
-        <v>16.78782445974707</v>
+        <v>13.29408937141863</v>
       </c>
       <c r="H93" t="n">
-        <v>18.22579593407363</v>
+        <v>15.96735853791741</v>
       </c>
       <c r="I93" t="n">
-        <v>16.23817669299988</v>
+        <v>13.60669201864794</v>
       </c>
       <c r="J93" t="n">
-        <v>19.63142468260304</v>
+        <v>16.25597289969985</v>
       </c>
       <c r="K93" t="n">
-        <v>20.13417976445841</v>
+        <v>14.54863832120095</v>
       </c>
       <c r="L93" t="n">
-        <v>22.20788920820744</v>
+        <v>18.57238026585078</v>
       </c>
       <c r="M93" t="n">
-        <v>19.31547100458919</v>
+        <v>14.45594307078746</v>
       </c>
       <c r="N93" t="n">
-        <v>22.16079516854324</v>
+        <v>18.56560524446975</v>
       </c>
       <c r="O93" t="n">
-        <v>23.02103484685506</v>
+        <v>16.45695836829307</v>
       </c>
       <c r="P93" t="n">
-        <v>26.05058261957638</v>
+        <v>23.22622414661366</v>
       </c>
       <c r="Q93" t="n">
-        <v>22.25196453592318</v>
+        <v>16.62575921121446</v>
       </c>
       <c r="R93" t="n">
-        <v>26.76335639535708</v>
+        <v>23.39097619742521</v>
       </c>
       <c r="S93" t="n">
-        <v>22.87285767945205</v>
+        <v>17.16664734480268</v>
       </c>
       <c r="T93" t="n">
-        <v>26.46367498316415</v>
+        <v>22.06644838492067</v>
       </c>
       <c r="U93" t="n">
-        <v>21.50043213225065</v>
+        <v>18.1759702582157</v>
       </c>
       <c r="V93" t="n">
-        <v>24.72515718871245</v>
+        <v>22.58837293163974</v>
       </c>
       <c r="W93" t="n">
-        <v>33.74561006809293</v>
+        <v>25.18360316851447</v>
       </c>
       <c r="X93" t="n">
-        <v>39.38116733818624</v>
+        <v>29.44989676305087</v>
       </c>
       <c r="Y93" t="n">
-        <v>33.50719892063818</v>
+        <v>25.24599529552493</v>
       </c>
       <c r="Z93" t="n">
-        <v>35.69583408964034</v>
+        <v>30.39414229140912</v>
       </c>
     </row>
     <row r="94">
@@ -8390,76 +8402,76 @@
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>124745734.0139234</v>
+        <v>9456492.33943055</v>
       </c>
       <c r="D94" t="n">
-        <v>79171147.89964367</v>
+        <v>66012226.88569013</v>
       </c>
       <c r="E94" t="n">
-        <v>59816668.62234961</v>
+        <v>13316148.48264034</v>
       </c>
       <c r="F94" t="n">
-        <v>71936596.07814094</v>
+        <v>64966721.23715408</v>
       </c>
       <c r="G94" t="n">
-        <v>60747122.77667988</v>
+        <v>7488079.741665149</v>
       </c>
       <c r="H94" t="n">
-        <v>72655183.21702753</v>
+        <v>63438709.48125646</v>
       </c>
       <c r="I94" t="n">
-        <v>73899305.54752588</v>
+        <v>12853769.23048269</v>
       </c>
       <c r="J94" t="n">
-        <v>87486394.74832633</v>
+        <v>67254912.87776434</v>
       </c>
       <c r="K94" t="n">
-        <v>126565808.2491749</v>
+        <v>10330220.27500739</v>
       </c>
       <c r="L94" t="n">
-        <v>120993818.9835209</v>
+        <v>62136994.58179553</v>
       </c>
       <c r="M94" t="n">
-        <v>54830892.33614475</v>
+        <v>9176505.735562218</v>
       </c>
       <c r="N94" t="n">
-        <v>67956146.26166096</v>
+        <v>59004710.30969592</v>
       </c>
       <c r="O94" t="n">
-        <v>71601993.52192226</v>
+        <v>9598679.011598114</v>
       </c>
       <c r="P94" t="n">
-        <v>83841814.61815603</v>
+        <v>69603282.78116648</v>
       </c>
       <c r="Q94" t="n">
-        <v>54827947.04890276</v>
+        <v>11426057.73462272</v>
       </c>
       <c r="R94" t="n">
-        <v>71936595.14831865</v>
+        <v>69137597.77791901</v>
       </c>
       <c r="S94" t="n">
-        <v>98587012.38929665</v>
+        <v>11130278.77789553</v>
       </c>
       <c r="T94" t="n">
-        <v>82932842.87349503</v>
+        <v>66299986.58404476</v>
       </c>
       <c r="U94" t="n">
-        <v>59284997.45468938</v>
+        <v>24470570.37553072</v>
       </c>
       <c r="V94" t="n">
-        <v>73393039.486756</v>
+        <v>70489318.22075821</v>
       </c>
       <c r="W94" t="n">
-        <v>148988628.1075687</v>
+        <v>9878975.041824162</v>
       </c>
       <c r="X94" t="n">
-        <v>71528994.98175563</v>
+        <v>57583618.14001675</v>
       </c>
       <c r="Y94" t="n">
-        <v>55748692.48361434</v>
+        <v>7408469.972569511</v>
       </c>
       <c r="Z94" t="n">
-        <v>80638765.17172419</v>
+        <v>70835533.4384184</v>
       </c>
     </row>
     <row r="95">
@@ -8472,76 +8484,76 @@
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>39.17313162592893</v>
+        <v>21.31455200780651</v>
       </c>
       <c r="D95" t="n">
-        <v>35.84324922207539</v>
+        <v>30.12443093709272</v>
       </c>
       <c r="E95" t="n">
-        <v>28.66969147839001</v>
+        <v>19.91345287608743</v>
       </c>
       <c r="F95" t="n">
-        <v>34.62559968342705</v>
+        <v>27.9576496385754</v>
       </c>
       <c r="G95" t="n">
-        <v>25.26503024567615</v>
+        <v>18.74543995888663</v>
       </c>
       <c r="H95" t="n">
-        <v>28.41132507405807</v>
+        <v>22.78372474923536</v>
       </c>
       <c r="I95" t="n">
-        <v>21.05067128507776</v>
+        <v>17.04874622426489</v>
       </c>
       <c r="J95" t="n">
-        <v>26.81258362852378</v>
+        <v>20.55992884779939</v>
       </c>
       <c r="K95" t="n">
-        <v>26.95706507001002</v>
+        <v>19.63708047822413</v>
       </c>
       <c r="L95" t="n">
-        <v>31.13936097856857</v>
+        <v>25.86889574640612</v>
       </c>
       <c r="M95" t="n">
-        <v>24.98047972633215</v>
+        <v>17.84674728612146</v>
       </c>
       <c r="N95" t="n">
-        <v>30.28896291358295</v>
+        <v>23.71162210396903</v>
       </c>
       <c r="O95" t="n">
-        <v>30.84726233099661</v>
+        <v>21.32589669191774</v>
       </c>
       <c r="P95" t="n">
-        <v>35.14727759408188</v>
+        <v>30.08867183513343</v>
       </c>
       <c r="Q95" t="n">
-        <v>27.73937911717459</v>
+        <v>19.80590182566831</v>
       </c>
       <c r="R95" t="n">
-        <v>34.62930224503175</v>
+        <v>27.87683217131071</v>
       </c>
       <c r="S95" t="n">
-        <v>29.96700391458885</v>
+        <v>22.22564297638642</v>
       </c>
       <c r="T95" t="n">
-        <v>36.07348328881261</v>
+        <v>28.89121411367045</v>
       </c>
       <c r="U95" t="n">
-        <v>26.78979329469495</v>
+        <v>21.52726749418352</v>
       </c>
       <c r="V95" t="n">
-        <v>31.54131531223148</v>
+        <v>26.9237869076467</v>
       </c>
       <c r="W95" t="n">
-        <v>40.64266352376126</v>
+        <v>30.47790554892729</v>
       </c>
       <c r="X95" t="n">
-        <v>51.12711713261799</v>
+        <v>36.97258313232422</v>
       </c>
       <c r="Y95" t="n">
-        <v>40.13408209988712</v>
+        <v>28.96882821429532</v>
       </c>
       <c r="Z95" t="n">
-        <v>42.73424527500071</v>
+        <v>34.8331577434112</v>
       </c>
     </row>
     <row r="96">
@@ -8636,76 +8648,76 @@
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>124745734.0139234</v>
+        <v>9456492.33943055</v>
       </c>
       <c r="D97" t="n">
-        <v>79171147.89964367</v>
+        <v>66012226.88569013</v>
       </c>
       <c r="E97" t="n">
-        <v>59816668.62234961</v>
+        <v>13316148.48264034</v>
       </c>
       <c r="F97" t="n">
-        <v>71936596.07814094</v>
+        <v>64966721.23715408</v>
       </c>
       <c r="G97" t="n">
-        <v>60747122.77667988</v>
+        <v>7488079.741665149</v>
       </c>
       <c r="H97" t="n">
-        <v>72655183.21702753</v>
+        <v>63438709.48125646</v>
       </c>
       <c r="I97" t="n">
-        <v>73899305.54752588</v>
+        <v>12853769.23048269</v>
       </c>
       <c r="J97" t="n">
-        <v>87486394.74832633</v>
+        <v>67254912.87776434</v>
       </c>
       <c r="K97" t="n">
-        <v>126565808.2491749</v>
+        <v>10330220.27500739</v>
       </c>
       <c r="L97" t="n">
-        <v>120993818.9835209</v>
+        <v>62136994.58179553</v>
       </c>
       <c r="M97" t="n">
-        <v>54830892.33614475</v>
+        <v>9176505.735562218</v>
       </c>
       <c r="N97" t="n">
-        <v>67956146.26166096</v>
+        <v>59004710.30969592</v>
       </c>
       <c r="O97" t="n">
-        <v>71601993.52192226</v>
+        <v>9598679.011598114</v>
       </c>
       <c r="P97" t="n">
-        <v>83841814.61815603</v>
+        <v>69603282.78116648</v>
       </c>
       <c r="Q97" t="n">
-        <v>54827947.04890276</v>
+        <v>11426057.73462272</v>
       </c>
       <c r="R97" t="n">
-        <v>71936595.14831865</v>
+        <v>69137597.77791901</v>
       </c>
       <c r="S97" t="n">
-        <v>98587012.38929665</v>
+        <v>11130278.77789553</v>
       </c>
       <c r="T97" t="n">
-        <v>82932842.87349503</v>
+        <v>66299986.58404476</v>
       </c>
       <c r="U97" t="n">
-        <v>59284997.45468938</v>
+        <v>24470570.37553072</v>
       </c>
       <c r="V97" t="n">
-        <v>73393039.486756</v>
+        <v>70489318.22075821</v>
       </c>
       <c r="W97" t="n">
-        <v>148988628.1075687</v>
+        <v>9878975.041824162</v>
       </c>
       <c r="X97" t="n">
-        <v>71528994.98175563</v>
+        <v>57583618.14001675</v>
       </c>
       <c r="Y97" t="n">
-        <v>55748692.48361434</v>
+        <v>7408469.972569511</v>
       </c>
       <c r="Z97" t="n">
-        <v>80638765.17172419</v>
+        <v>70835533.4384184</v>
       </c>
     </row>
     <row r="98">
@@ -8800,76 +8812,76 @@
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>13047045.84959497</v>
+        <v>1337560.84508124</v>
       </c>
       <c r="D99" t="n">
-        <v>12904986.98770971</v>
+        <v>11160570.96689028</v>
       </c>
       <c r="E99" t="n">
-        <v>10626985.04839166</v>
+        <v>1658420.06245598</v>
       </c>
       <c r="F99" t="n">
-        <v>11126590.03485534</v>
+        <v>11165777.34908655</v>
       </c>
       <c r="G99" t="n">
-        <v>10053629.7616131</v>
+        <v>1232303.756058337</v>
       </c>
       <c r="H99" t="n">
-        <v>12837675.81733143</v>
+        <v>11596766.25750731</v>
       </c>
       <c r="I99" t="n">
-        <v>12119751.75963238</v>
+        <v>1703445.096905015</v>
       </c>
       <c r="J99" t="n">
-        <v>13929819.18297177</v>
+        <v>12472109.74042984</v>
       </c>
       <c r="K99" t="n">
-        <v>16222795.17065103</v>
+        <v>1444536.955363726</v>
       </c>
       <c r="L99" t="n">
-        <v>17001682.97200233</v>
+        <v>11125742.38307261</v>
       </c>
       <c r="M99" t="n">
-        <v>9677640.548805989</v>
+        <v>1357763.83678517</v>
       </c>
       <c r="N99" t="n">
-        <v>11088979.55607712</v>
+        <v>10666426.02556751</v>
       </c>
       <c r="O99" t="n">
-        <v>10629696.8161987</v>
+        <v>1350735.106409079</v>
       </c>
       <c r="P99" t="n">
-        <v>13876832.81389271</v>
+        <v>11542919.08727382</v>
       </c>
       <c r="Q99" t="n">
-        <v>9013761.584616419</v>
+        <v>1512386.149575631</v>
       </c>
       <c r="R99" t="n">
-        <v>11126589.9975451</v>
+        <v>11806538.20451128</v>
       </c>
       <c r="S99" t="n">
-        <v>13815032.95809355</v>
+        <v>1506223.414025747</v>
       </c>
       <c r="T99" t="n">
-        <v>15397185.41170785</v>
+        <v>11804426.74348001</v>
       </c>
       <c r="U99" t="n">
-        <v>9934300.167555278</v>
+        <v>2402357.239630482</v>
       </c>
       <c r="V99" t="n">
-        <v>12257984.74620003</v>
+        <v>12792587.84367279</v>
       </c>
       <c r="W99" t="n">
-        <v>18372934.72248195</v>
+        <v>1438270.257768608</v>
       </c>
       <c r="X99" t="n">
-        <v>11733862.95378809</v>
+        <v>10462130.16103946</v>
       </c>
       <c r="Y99" t="n">
-        <v>9047065.105373295</v>
+        <v>1260930.60260424</v>
       </c>
       <c r="Z99" t="n">
-        <v>13212756.68037624</v>
+        <v>12537934.57246856</v>
       </c>
     </row>
     <row r="100">
@@ -9012,76 +9024,76 @@
         <v>1</v>
       </c>
       <c r="C101" t="n">
+        <v>4</v>
+      </c>
+      <c r="D101" t="n">
         <v>8</v>
       </c>
-      <c r="D101" t="n">
-        <v>9</v>
-      </c>
       <c r="E101" t="n">
+        <v>4</v>
+      </c>
+      <c r="F101" t="n">
         <v>8</v>
       </c>
-      <c r="F101" t="n">
-        <v>9</v>
-      </c>
       <c r="G101" t="n">
+        <v>4</v>
+      </c>
+      <c r="H101" t="n">
         <v>8</v>
       </c>
-      <c r="H101" t="n">
-        <v>9</v>
-      </c>
       <c r="I101" t="n">
+        <v>4</v>
+      </c>
+      <c r="J101" t="n">
         <v>8</v>
       </c>
-      <c r="J101" t="n">
-        <v>9</v>
-      </c>
       <c r="K101" t="n">
+        <v>4</v>
+      </c>
+      <c r="L101" t="n">
         <v>8</v>
       </c>
-      <c r="L101" t="n">
-        <v>9</v>
-      </c>
       <c r="M101" t="n">
+        <v>4</v>
+      </c>
+      <c r="N101" t="n">
         <v>8</v>
       </c>
-      <c r="N101" t="n">
-        <v>9</v>
-      </c>
       <c r="O101" t="n">
+        <v>4</v>
+      </c>
+      <c r="P101" t="n">
         <v>8</v>
       </c>
-      <c r="P101" t="n">
-        <v>9</v>
-      </c>
       <c r="Q101" t="n">
+        <v>4</v>
+      </c>
+      <c r="R101" t="n">
         <v>8</v>
       </c>
-      <c r="R101" t="n">
-        <v>9</v>
-      </c>
       <c r="S101" t="n">
+        <v>4</v>
+      </c>
+      <c r="T101" t="n">
         <v>8</v>
       </c>
-      <c r="T101" t="n">
-        <v>9</v>
-      </c>
       <c r="U101" t="n">
+        <v>4</v>
+      </c>
+      <c r="V101" t="n">
         <v>8</v>
       </c>
-      <c r="V101" t="n">
-        <v>9</v>
-      </c>
       <c r="W101" t="n">
+        <v>4</v>
+      </c>
+      <c r="X101" t="n">
         <v>8</v>
       </c>
-      <c r="X101" t="n">
-        <v>9</v>
-      </c>
       <c r="Y101" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z101" t="n">
         <v>8</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="102">
@@ -9094,76 +9106,76 @@
         <v>1</v>
       </c>
       <c r="C102" t="n">
+        <v>4</v>
+      </c>
+      <c r="D102" t="n">
         <v>8</v>
       </c>
-      <c r="D102" t="n">
-        <v>9</v>
-      </c>
       <c r="E102" t="n">
+        <v>4</v>
+      </c>
+      <c r="F102" t="n">
         <v>8</v>
       </c>
-      <c r="F102" t="n">
-        <v>9</v>
-      </c>
       <c r="G102" t="n">
+        <v>4</v>
+      </c>
+      <c r="H102" t="n">
         <v>8</v>
       </c>
-      <c r="H102" t="n">
-        <v>9</v>
-      </c>
       <c r="I102" t="n">
+        <v>4</v>
+      </c>
+      <c r="J102" t="n">
         <v>8</v>
       </c>
-      <c r="J102" t="n">
-        <v>9</v>
-      </c>
       <c r="K102" t="n">
+        <v>4</v>
+      </c>
+      <c r="L102" t="n">
         <v>8</v>
       </c>
-      <c r="L102" t="n">
-        <v>9</v>
-      </c>
       <c r="M102" t="n">
+        <v>4</v>
+      </c>
+      <c r="N102" t="n">
         <v>8</v>
       </c>
-      <c r="N102" t="n">
-        <v>9</v>
-      </c>
       <c r="O102" t="n">
+        <v>4</v>
+      </c>
+      <c r="P102" t="n">
         <v>8</v>
       </c>
-      <c r="P102" t="n">
-        <v>9</v>
-      </c>
       <c r="Q102" t="n">
+        <v>4</v>
+      </c>
+      <c r="R102" t="n">
         <v>8</v>
       </c>
-      <c r="R102" t="n">
-        <v>9</v>
-      </c>
       <c r="S102" t="n">
+        <v>4</v>
+      </c>
+      <c r="T102" t="n">
         <v>8</v>
       </c>
-      <c r="T102" t="n">
-        <v>9</v>
-      </c>
       <c r="U102" t="n">
+        <v>4</v>
+      </c>
+      <c r="V102" t="n">
         <v>8</v>
       </c>
-      <c r="V102" t="n">
-        <v>9</v>
-      </c>
       <c r="W102" t="n">
+        <v>4</v>
+      </c>
+      <c r="X102" t="n">
         <v>8</v>
       </c>
-      <c r="X102" t="n">
-        <v>9</v>
-      </c>
       <c r="Y102" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z102" t="n">
         <v>8</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="103">
@@ -15362,76 +15374,76 @@
         <v>0</v>
       </c>
       <c r="C172" t="n">
+        <v>4</v>
+      </c>
+      <c r="D172" t="n">
         <v>8</v>
       </c>
-      <c r="D172" t="n">
-        <v>9</v>
-      </c>
       <c r="E172" t="n">
+        <v>4</v>
+      </c>
+      <c r="F172" t="n">
         <v>8</v>
       </c>
-      <c r="F172" t="n">
-        <v>9</v>
-      </c>
       <c r="G172" t="n">
+        <v>4</v>
+      </c>
+      <c r="H172" t="n">
         <v>8</v>
       </c>
-      <c r="H172" t="n">
-        <v>9</v>
-      </c>
       <c r="I172" t="n">
+        <v>4</v>
+      </c>
+      <c r="J172" t="n">
         <v>8</v>
       </c>
-      <c r="J172" t="n">
-        <v>9</v>
-      </c>
       <c r="K172" t="n">
+        <v>4</v>
+      </c>
+      <c r="L172" t="n">
         <v>8</v>
       </c>
-      <c r="L172" t="n">
-        <v>9</v>
-      </c>
       <c r="M172" t="n">
+        <v>4</v>
+      </c>
+      <c r="N172" t="n">
         <v>8</v>
       </c>
-      <c r="N172" t="n">
-        <v>9</v>
-      </c>
       <c r="O172" t="n">
+        <v>4</v>
+      </c>
+      <c r="P172" t="n">
         <v>8</v>
       </c>
-      <c r="P172" t="n">
-        <v>9</v>
-      </c>
       <c r="Q172" t="n">
+        <v>4</v>
+      </c>
+      <c r="R172" t="n">
         <v>8</v>
       </c>
-      <c r="R172" t="n">
-        <v>9</v>
-      </c>
       <c r="S172" t="n">
+        <v>4</v>
+      </c>
+      <c r="T172" t="n">
         <v>8</v>
       </c>
-      <c r="T172" t="n">
-        <v>9</v>
-      </c>
       <c r="U172" t="n">
+        <v>4</v>
+      </c>
+      <c r="V172" t="n">
         <v>8</v>
       </c>
-      <c r="V172" t="n">
-        <v>9</v>
-      </c>
       <c r="W172" t="n">
+        <v>4</v>
+      </c>
+      <c r="X172" t="n">
         <v>8</v>
       </c>
-      <c r="X172" t="n">
-        <v>9</v>
-      </c>
       <c r="Y172" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z172" t="n">
         <v>8</v>
-      </c>
-      <c r="Z172" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="173">
@@ -15444,76 +15456,76 @@
         <v>0</v>
       </c>
       <c r="C173" t="n">
-        <v>3876.752682194626</v>
+        <v>5530.471188868572</v>
       </c>
       <c r="D173" t="n">
-        <v>4734.581514287972</v>
+        <v>6470.006167784558</v>
       </c>
       <c r="E173" t="n">
-        <v>5437.444755671272</v>
+        <v>5636.214559652709</v>
       </c>
       <c r="F173" t="n">
-        <v>3695.215237941936</v>
+        <v>6295.763366915544</v>
       </c>
       <c r="G173" t="n">
-        <v>4266.118815841311</v>
+        <v>5452.054445425456</v>
       </c>
       <c r="H173" t="n">
-        <v>3970.748007805056</v>
+        <v>6029.167859465953</v>
       </c>
       <c r="I173" t="n">
-        <v>5021.342697402944</v>
+        <v>5584.76627259995</v>
       </c>
       <c r="J173" t="n">
-        <v>3769.842392701432</v>
+        <v>6675.789222825592</v>
       </c>
       <c r="K173" t="n">
-        <v>5858.367721872341</v>
+        <v>5537.520475815752</v>
       </c>
       <c r="L173" t="n">
-        <v>4909.201745508964</v>
+        <v>5823.853144940669</v>
       </c>
       <c r="M173" t="n">
-        <v>4606.482053422182</v>
+        <v>5503.044685260468</v>
       </c>
       <c r="N173" t="n">
-        <v>3397.574350004056</v>
+        <v>5302.108290008699</v>
       </c>
       <c r="O173" t="n">
-        <v>4998.238027968651</v>
+        <v>5534.849832424019</v>
       </c>
       <c r="P173" t="n">
-        <v>5282.105501708679</v>
+        <v>6735.210663058917</v>
       </c>
       <c r="Q173" t="n">
-        <v>4605.792729004864</v>
+        <v>5590.147855873176</v>
       </c>
       <c r="R173" t="n">
-        <v>3695.215174235857</v>
+        <v>6989.770279265924</v>
       </c>
       <c r="S173" t="n">
-        <v>5483.699076105475</v>
+        <v>5561.120671043826</v>
       </c>
       <c r="T173" t="n">
-        <v>5175.236410570927</v>
+        <v>6517.950008304651</v>
       </c>
       <c r="U173" t="n">
-        <v>4583.614639954812</v>
+        <v>5504.184886217874</v>
       </c>
       <c r="V173" t="n">
-        <v>4059.04617822482</v>
+        <v>7214.816418236726</v>
       </c>
       <c r="W173" t="n">
-        <v>5541.416350622969</v>
+        <v>5506.924792348185</v>
       </c>
       <c r="X173" t="n">
-        <v>3840.848116453827</v>
+        <v>5046.670002692638</v>
       </c>
       <c r="Y173" t="n">
-        <v>3633.854304778129</v>
+        <v>5345.95672530144</v>
       </c>
       <c r="Z173" t="n">
-        <v>3768.48668057022</v>
+        <v>6163.96119650579</v>
       </c>
     </row>
     <row r="174">
@@ -15690,76 +15702,76 @@
         <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>7808.752682194626</v>
+        <v>9462.471188868572</v>
       </c>
       <c r="D176" t="n">
-        <v>8666.581514287973</v>
+        <v>10402.00616778456</v>
       </c>
       <c r="E176" t="n">
-        <v>9369.444755671273</v>
+        <v>9568.214559652708</v>
       </c>
       <c r="F176" t="n">
-        <v>7627.215237941936</v>
+        <v>10227.76336691554</v>
       </c>
       <c r="G176" t="n">
-        <v>8198.11881584131</v>
+        <v>9384.054445425456</v>
       </c>
       <c r="H176" t="n">
-        <v>7902.748007805056</v>
+        <v>9961.167859465953</v>
       </c>
       <c r="I176" t="n">
-        <v>8953.342697402944</v>
+        <v>9516.766272599951</v>
       </c>
       <c r="J176" t="n">
-        <v>7701.842392701432</v>
+        <v>10607.78922282559</v>
       </c>
       <c r="K176" t="n">
-        <v>9790.367721872342</v>
+        <v>9469.520475815752</v>
       </c>
       <c r="L176" t="n">
-        <v>8841.201745508963</v>
+        <v>9755.853144940669</v>
       </c>
       <c r="M176" t="n">
-        <v>8538.482053422182</v>
+        <v>9435.044685260469</v>
       </c>
       <c r="N176" t="n">
-        <v>7329.574350004056</v>
+        <v>9234.108290008699</v>
       </c>
       <c r="O176" t="n">
-        <v>8930.238027968651</v>
+        <v>9466.849832424019</v>
       </c>
       <c r="P176" t="n">
-        <v>9214.10550170868</v>
+        <v>10667.21066305892</v>
       </c>
       <c r="Q176" t="n">
-        <v>8537.792729004865</v>
+        <v>9522.147855873176</v>
       </c>
       <c r="R176" t="n">
-        <v>7627.215174235857</v>
+        <v>10921.77027926592</v>
       </c>
       <c r="S176" t="n">
-        <v>9415.699076105475</v>
+        <v>9493.120671043827</v>
       </c>
       <c r="T176" t="n">
-        <v>9107.236410570928</v>
+        <v>10449.95000830465</v>
       </c>
       <c r="U176" t="n">
-        <v>8515.614639954812</v>
+        <v>9436.184886217874</v>
       </c>
       <c r="V176" t="n">
-        <v>7991.04617822482</v>
+        <v>11146.81641823673</v>
       </c>
       <c r="W176" t="n">
-        <v>9473.416350622969</v>
+        <v>9438.924792348185</v>
       </c>
       <c r="X176" t="n">
-        <v>7772.848116453826</v>
+        <v>8978.670002692637</v>
       </c>
       <c r="Y176" t="n">
-        <v>7565.854304778129</v>
+        <v>9277.956725301439</v>
       </c>
       <c r="Z176" t="n">
-        <v>7700.48668057022</v>
+        <v>10095.96119650579</v>
       </c>
     </row>
     <row r="177">
@@ -16100,76 +16112,76 @@
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>9808.752682194627</v>
+        <v>11462.47118886857</v>
       </c>
       <c r="D181" t="n">
-        <v>10666.58151428797</v>
+        <v>12402.00616778456</v>
       </c>
       <c r="E181" t="n">
-        <v>11369.44475567127</v>
+        <v>11568.21455965271</v>
       </c>
       <c r="F181" t="n">
-        <v>9627.215237941935</v>
+        <v>12227.76336691554</v>
       </c>
       <c r="G181" t="n">
-        <v>10198.11881584131</v>
+        <v>11384.05444542546</v>
       </c>
       <c r="H181" t="n">
-        <v>9902.748007805056</v>
+        <v>11961.16785946595</v>
       </c>
       <c r="I181" t="n">
-        <v>10953.34269740294</v>
+        <v>11516.76627259995</v>
       </c>
       <c r="J181" t="n">
-        <v>9701.842392701432</v>
+        <v>12607.78922282559</v>
       </c>
       <c r="K181" t="n">
-        <v>11790.36772187234</v>
+        <v>11469.52047581575</v>
       </c>
       <c r="L181" t="n">
-        <v>10841.20174550896</v>
+        <v>11755.85314494067</v>
       </c>
       <c r="M181" t="n">
-        <v>10538.48205342218</v>
+        <v>11435.04468526047</v>
       </c>
       <c r="N181" t="n">
-        <v>9329.574350004055</v>
+        <v>11234.1082900087</v>
       </c>
       <c r="O181" t="n">
-        <v>10930.23802796865</v>
+        <v>11466.84983242402</v>
       </c>
       <c r="P181" t="n">
-        <v>11214.10550170868</v>
+        <v>12667.21066305892</v>
       </c>
       <c r="Q181" t="n">
-        <v>10537.79272900486</v>
+        <v>11522.14785587318</v>
       </c>
       <c r="R181" t="n">
-        <v>9627.215174235858</v>
+        <v>12921.77027926592</v>
       </c>
       <c r="S181" t="n">
-        <v>11415.69907610547</v>
+        <v>11493.12067104383</v>
       </c>
       <c r="T181" t="n">
-        <v>11107.23641057093</v>
+        <v>12449.95000830465</v>
       </c>
       <c r="U181" t="n">
-        <v>10515.61463995481</v>
+        <v>11436.18488621787</v>
       </c>
       <c r="V181" t="n">
-        <v>9991.04617822482</v>
+        <v>13146.81641823673</v>
       </c>
       <c r="W181" t="n">
-        <v>11473.41635062297</v>
+        <v>11438.92479234819</v>
       </c>
       <c r="X181" t="n">
-        <v>9772.848116453826</v>
+        <v>10978.67000269264</v>
       </c>
       <c r="Y181" t="n">
-        <v>9565.854304778128</v>
+        <v>11277.95672530144</v>
       </c>
       <c r="Z181" t="n">
-        <v>9700.48668057022</v>
+        <v>12095.96119650579</v>
       </c>
     </row>
     <row r="182">
@@ -16182,76 +16194,76 @@
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>8808.752682194627</v>
+        <v>10462.47118886857</v>
       </c>
       <c r="D182" t="n">
-        <v>9666.581514287973</v>
+        <v>11402.00616778456</v>
       </c>
       <c r="E182" t="n">
-        <v>10369.44475567127</v>
+        <v>10568.21455965271</v>
       </c>
       <c r="F182" t="n">
-        <v>8627.215237941935</v>
+        <v>11227.76336691554</v>
       </c>
       <c r="G182" t="n">
-        <v>9198.11881584131</v>
+        <v>10384.05444542546</v>
       </c>
       <c r="H182" t="n">
-        <v>8902.748007805056</v>
+        <v>10961.16785946595</v>
       </c>
       <c r="I182" t="n">
-        <v>9953.342697402944</v>
+        <v>10516.76627259995</v>
       </c>
       <c r="J182" t="n">
-        <v>8701.842392701432</v>
+        <v>11607.78922282559</v>
       </c>
       <c r="K182" t="n">
-        <v>10790.36772187234</v>
+        <v>10469.52047581575</v>
       </c>
       <c r="L182" t="n">
-        <v>9841.201745508963</v>
+        <v>10755.85314494067</v>
       </c>
       <c r="M182" t="n">
-        <v>9538.482053422182</v>
+        <v>10435.04468526047</v>
       </c>
       <c r="N182" t="n">
-        <v>8329.574350004055</v>
+        <v>10234.1082900087</v>
       </c>
       <c r="O182" t="n">
-        <v>9930.238027968651</v>
+        <v>10466.84983242402</v>
       </c>
       <c r="P182" t="n">
-        <v>10214.10550170868</v>
+        <v>11667.21066305892</v>
       </c>
       <c r="Q182" t="n">
-        <v>9537.792729004865</v>
+        <v>10522.14785587318</v>
       </c>
       <c r="R182" t="n">
-        <v>8627.215174235858</v>
+        <v>11921.77027926592</v>
       </c>
       <c r="S182" t="n">
-        <v>10415.69907610547</v>
+        <v>10493.12067104383</v>
       </c>
       <c r="T182" t="n">
-        <v>10107.23641057093</v>
+        <v>11449.95000830465</v>
       </c>
       <c r="U182" t="n">
-        <v>9515.614639954812</v>
+        <v>10436.18488621787</v>
       </c>
       <c r="V182" t="n">
-        <v>8991.04617822482</v>
+        <v>12146.81641823673</v>
       </c>
       <c r="W182" t="n">
-        <v>10473.41635062297</v>
+        <v>10438.92479234819</v>
       </c>
       <c r="X182" t="n">
-        <v>8772.848116453826</v>
+        <v>9978.670002692637</v>
       </c>
       <c r="Y182" t="n">
-        <v>8565.854304778128</v>
+        <v>10277.95672530144</v>
       </c>
       <c r="Z182" t="n">
-        <v>8700.48668057022</v>
+        <v>11095.96119650579</v>
       </c>
     </row>
     <row r="183">
@@ -16264,76 +16276,76 @@
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>8408.752682194627</v>
+        <v>10062.47118886857</v>
       </c>
       <c r="D183" t="n">
-        <v>9266.581514287973</v>
+        <v>11002.00616778456</v>
       </c>
       <c r="E183" t="n">
-        <v>9969.444755671273</v>
+        <v>10168.21455965271</v>
       </c>
       <c r="F183" t="n">
-        <v>8227.215237941935</v>
+        <v>10827.76336691554</v>
       </c>
       <c r="G183" t="n">
-        <v>8798.11881584131</v>
+        <v>9984.054445425456</v>
       </c>
       <c r="H183" t="n">
-        <v>8502.748007805056</v>
+        <v>10561.16785946595</v>
       </c>
       <c r="I183" t="n">
-        <v>9553.342697402944</v>
+        <v>10116.76627259995</v>
       </c>
       <c r="J183" t="n">
-        <v>8301.842392701432</v>
+        <v>11207.78922282559</v>
       </c>
       <c r="K183" t="n">
-        <v>10390.36772187234</v>
+        <v>10069.52047581575</v>
       </c>
       <c r="L183" t="n">
-        <v>9441.201745508963</v>
+        <v>10355.85314494067</v>
       </c>
       <c r="M183" t="n">
-        <v>9138.482053422182</v>
+        <v>10035.04468526047</v>
       </c>
       <c r="N183" t="n">
-        <v>7929.574350004056</v>
+        <v>9834.108290008699</v>
       </c>
       <c r="O183" t="n">
-        <v>9530.238027968651</v>
+        <v>10066.84983242402</v>
       </c>
       <c r="P183" t="n">
-        <v>9814.10550170868</v>
+        <v>11267.21066305892</v>
       </c>
       <c r="Q183" t="n">
-        <v>9137.792729004865</v>
+        <v>10122.14785587318</v>
       </c>
       <c r="R183" t="n">
-        <v>8227.215174235858</v>
+        <v>11521.77027926592</v>
       </c>
       <c r="S183" t="n">
-        <v>10015.69907610547</v>
+        <v>10093.12067104383</v>
       </c>
       <c r="T183" t="n">
-        <v>9707.236410570928</v>
+        <v>11049.95000830465</v>
       </c>
       <c r="U183" t="n">
-        <v>9115.614639954812</v>
+        <v>10036.18488621787</v>
       </c>
       <c r="V183" t="n">
-        <v>8591.04617822482</v>
+        <v>11746.81641823673</v>
       </c>
       <c r="W183" t="n">
-        <v>10073.41635062297</v>
+        <v>10038.92479234819</v>
       </c>
       <c r="X183" t="n">
-        <v>8372.848116453826</v>
+        <v>9578.670002692637</v>
       </c>
       <c r="Y183" t="n">
-        <v>8165.854304778129</v>
+        <v>9877.956725301439</v>
       </c>
       <c r="Z183" t="n">
-        <v>8300.48668057022</v>
+        <v>10695.96119650579</v>
       </c>
     </row>
     <row r="184">
@@ -16346,76 +16358,76 @@
         <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>840.8752682194627</v>
+        <v>1006.247118886857</v>
       </c>
       <c r="D184" t="n">
-        <v>926.6581514287973</v>
+        <v>1100.200616778456</v>
       </c>
       <c r="E184" t="n">
-        <v>996.9444755671273</v>
+        <v>1016.821455965271</v>
       </c>
       <c r="F184" t="n">
-        <v>822.7215237941934</v>
+        <v>1082.776336691554</v>
       </c>
       <c r="G184" t="n">
-        <v>879.811881584131</v>
+        <v>998.4054445425456</v>
       </c>
       <c r="H184" t="n">
-        <v>850.2748007805055</v>
+        <v>1056.116785946595</v>
       </c>
       <c r="I184" t="n">
-        <v>955.3342697402944</v>
+        <v>1011.676627259995</v>
       </c>
       <c r="J184" t="n">
-        <v>830.1842392701432</v>
+        <v>1120.778922282559</v>
       </c>
       <c r="K184" t="n">
-        <v>1039.036772187234</v>
+        <v>1006.952047581575</v>
       </c>
       <c r="L184" t="n">
-        <v>944.1201745508963</v>
+        <v>1035.585314494067</v>
       </c>
       <c r="M184" t="n">
-        <v>913.8482053422182</v>
+        <v>1003.504468526047</v>
       </c>
       <c r="N184" t="n">
-        <v>792.9574350004057</v>
+        <v>983.4108290008699</v>
       </c>
       <c r="O184" t="n">
-        <v>953.0238027968651</v>
+        <v>1006.684983242402</v>
       </c>
       <c r="P184" t="n">
-        <v>981.410550170868</v>
+        <v>1126.721066305892</v>
       </c>
       <c r="Q184" t="n">
-        <v>913.7792729004865</v>
+        <v>1012.214785587318</v>
       </c>
       <c r="R184" t="n">
-        <v>822.7215174235859</v>
+        <v>1152.177027926592</v>
       </c>
       <c r="S184" t="n">
-        <v>1001.569907610547</v>
+        <v>1009.312067104383</v>
       </c>
       <c r="T184" t="n">
-        <v>970.7236410570928</v>
+        <v>1104.995000830465</v>
       </c>
       <c r="U184" t="n">
-        <v>911.5614639954813</v>
+        <v>1003.618488621787</v>
       </c>
       <c r="V184" t="n">
-        <v>859.1046178224821</v>
+        <v>1174.681641823673</v>
       </c>
       <c r="W184" t="n">
-        <v>1007.341635062297</v>
+        <v>1003.892479234819</v>
       </c>
       <c r="X184" t="n">
-        <v>837.2848116453827</v>
+        <v>957.8670002692637</v>
       </c>
       <c r="Y184" t="n">
-        <v>816.5854304778129</v>
+        <v>987.795672530144</v>
       </c>
       <c r="Z184" t="n">
-        <v>830.048668057022</v>
+        <v>1069.596119650579</v>
       </c>
     </row>
     <row r="185">
@@ -16428,76 +16440,76 @@
         <v>0</v>
       </c>
       <c r="C185" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="D185" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="D185" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="E185" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="F185" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="F185" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="G185" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="H185" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="H185" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="I185" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="J185" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="J185" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="K185" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="L185" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="L185" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="M185" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="N185" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="N185" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="O185" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="P185" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="P185" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="Q185" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="R185" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="R185" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="S185" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="T185" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="T185" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="U185" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="V185" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="V185" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="W185" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="X185" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="X185" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="Y185" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="Z185" t="n">
         <v>0.02285714285714286</v>
-      </c>
-      <c r="Z185" t="n">
-        <v>0.02571428571428571</v>
       </c>
     </row>
     <row r="186">
@@ -16510,76 +16522,76 @@
         <v>0</v>
       </c>
       <c r="C186" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="D186" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="D186" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="E186" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="F186" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="F186" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="G186" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="H186" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="H186" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="I186" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="J186" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="J186" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="K186" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="L186" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="L186" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="M186" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="N186" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="N186" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="O186" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="P186" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="P186" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="Q186" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="R186" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="R186" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="S186" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="T186" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="T186" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="U186" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="V186" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="V186" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="W186" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="X186" t="n">
         <v>0.02285714285714286</v>
       </c>
-      <c r="X186" t="n">
-        <v>0.02571428571428571</v>
-      </c>
       <c r="Y186" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="Z186" t="n">
         <v>0.02285714285714286</v>
-      </c>
-      <c r="Z186" t="n">
-        <v>0.02571428571428571</v>
       </c>
     </row>
     <row r="187">
@@ -16592,76 +16604,76 @@
         <v>0</v>
       </c>
       <c r="C187" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="D187" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="D187" t="n">
-        <v>0.03</v>
-      </c>
       <c r="E187" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="F187" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="F187" t="n">
-        <v>0.03</v>
-      </c>
       <c r="G187" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="H187" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="H187" t="n">
-        <v>0.03</v>
-      </c>
       <c r="I187" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="J187" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="J187" t="n">
-        <v>0.03</v>
-      </c>
       <c r="K187" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="L187" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="L187" t="n">
-        <v>0.03</v>
-      </c>
       <c r="M187" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="N187" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="N187" t="n">
-        <v>0.03</v>
-      </c>
       <c r="O187" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="P187" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="P187" t="n">
-        <v>0.03</v>
-      </c>
       <c r="Q187" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="R187" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="R187" t="n">
-        <v>0.03</v>
-      </c>
       <c r="S187" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="T187" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="T187" t="n">
-        <v>0.03</v>
-      </c>
       <c r="U187" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="V187" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="V187" t="n">
-        <v>0.03</v>
-      </c>
       <c r="W187" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="X187" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="X187" t="n">
-        <v>0.03</v>
-      </c>
       <c r="Y187" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="Z187" t="n">
         <v>0.02666666666666667</v>
-      </c>
-      <c r="Z187" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="188">
@@ -16674,76 +16686,76 @@
         <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>13541.81617784895</v>
+        <v>15831.55101884647</v>
       </c>
       <c r="D188" t="n">
-        <v>14699.88516573705</v>
+        <v>17047.87957768459</v>
       </c>
       <c r="E188" t="n">
-        <v>15648.88528358617</v>
+        <v>15917.08965622202</v>
       </c>
       <c r="F188" t="n">
-        <v>13296.74914681686</v>
+        <v>16820.33544630033</v>
       </c>
       <c r="G188" t="n">
-        <v>14067.46612776962</v>
+        <v>15762.79644376088</v>
       </c>
       <c r="H188" t="n">
-        <v>13668.68913582228</v>
+        <v>16447.58423888239</v>
       </c>
       <c r="I188" t="n">
-        <v>15087.01264261912</v>
+        <v>15915.44969605259</v>
       </c>
       <c r="J188" t="n">
-        <v>13397.48723651953</v>
+        <v>17320.52736419528</v>
       </c>
       <c r="K188" t="n">
-        <v>16217.031663266</v>
+        <v>15865.4431978031</v>
       </c>
       <c r="L188" t="n">
-        <v>14935.63866381537</v>
+        <v>16170.44576145638</v>
       </c>
       <c r="M188" t="n">
-        <v>14616.83675885998</v>
+        <v>15759.13488051215</v>
       </c>
       <c r="N188" t="n">
-        <v>12894.9253806916</v>
+        <v>15520.44903884894</v>
       </c>
       <c r="O188" t="n">
-        <v>15055.82134874959</v>
+        <v>15855.42928915157</v>
       </c>
       <c r="P188" t="n">
-        <v>15459.53467044235</v>
+        <v>17400.73536862789</v>
       </c>
       <c r="Q188" t="n">
-        <v>14526.0766421633</v>
+        <v>15856.00025771707</v>
       </c>
       <c r="R188" t="n">
-        <v>13296.74861313434</v>
+        <v>17744.76988344986</v>
       </c>
       <c r="S188" t="n">
-        <v>15711.250533759</v>
+        <v>15815.71290612589</v>
       </c>
       <c r="T188" t="n">
-        <v>15294.76919379826</v>
+        <v>17107.43407530331</v>
       </c>
       <c r="U188" t="n">
-        <v>14496.16720690176</v>
+        <v>15738.98965341911</v>
       </c>
       <c r="V188" t="n">
-        <v>13788.67673847747</v>
+        <v>18048.21123111161</v>
       </c>
       <c r="W188" t="n">
-        <v>15789.11207626734</v>
+        <v>15851.60753087</v>
       </c>
       <c r="X188" t="n">
-        <v>13505.52525552601</v>
+        <v>15121.20649908066</v>
       </c>
       <c r="Y188" t="n">
-        <v>13216.83847732706</v>
+        <v>15619.45598363775</v>
       </c>
       <c r="Z188" t="n">
-        <v>13395.6570193861</v>
+        <v>16629.54761917911</v>
       </c>
     </row>
     <row r="189">
@@ -16838,76 +16850,76 @@
         <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>78470.02145755701</v>
+        <v>22924.94237773714</v>
       </c>
       <c r="D190" t="n">
-        <v>107999.1378321657</v>
+        <v>99216.04934227647</v>
       </c>
       <c r="E190" t="n">
-        <v>90955.55804537018</v>
+        <v>23136.42911930542</v>
       </c>
       <c r="F190" t="n">
-        <v>97475.55428416209</v>
+        <v>97822.10693532435</v>
       </c>
       <c r="G190" t="n">
-        <v>81584.95052673048</v>
+        <v>22768.10889085091</v>
       </c>
       <c r="H190" t="n">
-        <v>100265.3235790262</v>
+        <v>95689.34287572763</v>
       </c>
       <c r="I190" t="n">
-        <v>87626.74157922356</v>
+        <v>23033.5325451999</v>
       </c>
       <c r="J190" t="n">
-        <v>98231.15422610199</v>
+        <v>100862.3137826047</v>
       </c>
       <c r="K190" t="n">
-        <v>94322.94177497874</v>
+        <v>22939.0409516315</v>
       </c>
       <c r="L190" t="n">
-        <v>109767.1676732783</v>
+        <v>94046.82515952535</v>
       </c>
       <c r="M190" t="n">
-        <v>84307.85642737745</v>
+        <v>22870.08937052094</v>
       </c>
       <c r="N190" t="n">
-        <v>94461.94029379106</v>
+        <v>89872.86632006959</v>
       </c>
       <c r="O190" t="n">
-        <v>87441.90422374921</v>
+        <v>22933.69966484804</v>
       </c>
       <c r="P190" t="n">
-        <v>113542.8182048004</v>
+        <v>101337.6853044713</v>
       </c>
       <c r="Q190" t="n">
-        <v>84302.34183203892</v>
+        <v>23044.29571174635</v>
       </c>
       <c r="R190" t="n">
-        <v>97475.55363913806</v>
+        <v>103374.1622341274</v>
       </c>
       <c r="S190" t="n">
-        <v>91325.5926088438</v>
+        <v>22986.24134208765</v>
       </c>
       <c r="T190" t="n">
-        <v>112460.7686570306</v>
+        <v>99599.60006643721</v>
       </c>
       <c r="U190" t="n">
-        <v>84124.9171196385</v>
+        <v>22872.36977243575</v>
       </c>
       <c r="V190" t="n">
-        <v>101159.3425545263</v>
+        <v>105174.5313458938</v>
       </c>
       <c r="W190" t="n">
-        <v>91787.33080498375</v>
+        <v>22877.84958469637</v>
       </c>
       <c r="X190" t="n">
-        <v>98950.08717909499</v>
+        <v>87829.3600215411</v>
       </c>
       <c r="Y190" t="n">
-        <v>76526.83443822502</v>
+        <v>22555.91345060288</v>
       </c>
       <c r="Z190" t="n">
-        <v>98217.42764077349</v>
+        <v>96767.68957204632</v>
       </c>
     </row>
     <row r="191">
@@ -17051,122 +17063,122 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>&lt;built-in method __new__ of type object at 0x00007FFE381E0360&gt;</t>
+          <t>&lt;built-in method __new__ of type object at 0x00007FFC55E5C360&gt;</t>
         </is>
       </c>
     </row>
@@ -23358,76 +23370,76 @@
         <v>0</v>
       </c>
       <c r="C242" t="n">
-        <v>0.007361109059368197</v>
+        <v>0.007234868081813203</v>
       </c>
       <c r="D242" t="n">
-        <v>0.02042984400034291</v>
+        <v>0.01810089909504388</v>
       </c>
       <c r="E242" t="n">
-        <v>0.01813442304496663</v>
+        <v>0.005190797510841457</v>
       </c>
       <c r="F242" t="n">
-        <v>0.02001580290206089</v>
+        <v>0.0181061124332213</v>
       </c>
       <c r="G242" t="n">
-        <v>0.01579991440721967</v>
+        <v>0.009066903484622699</v>
       </c>
       <c r="H242" t="n">
-        <v>0.02046579499984779</v>
+        <v>0.01809396682870491</v>
       </c>
       <c r="I242" t="n">
-        <v>0.01407802883506905</v>
+        <v>0.00535083838709544</v>
       </c>
       <c r="J242" t="n">
-        <v>0.01660394718223613</v>
+        <v>0.01809281728825249</v>
       </c>
       <c r="K242" t="n">
-        <v>0.008925311182325164</v>
+        <v>0.006627493704505994</v>
       </c>
       <c r="L242" t="n">
-        <v>0.01361465997458042</v>
+        <v>0.01812056853363724</v>
       </c>
       <c r="M242" t="n">
-        <v>0.01816685284380091</v>
+        <v>0.007435687744479932</v>
       </c>
       <c r="N242" t="n">
-        <v>0.02043985818603385</v>
+        <v>0.01813931258453644</v>
       </c>
       <c r="O242" t="n">
-        <v>0.01449529552552034</v>
+        <v>0.007130738038722865</v>
       </c>
       <c r="P242" t="n">
-        <v>0.02040752356086872</v>
+        <v>0.01757344033956859</v>
       </c>
       <c r="Q242" t="n">
-        <v>0.01816648767714746</v>
+        <v>0.00602257757114569</v>
       </c>
       <c r="R242" t="n">
-        <v>0.02001580300946602</v>
+        <v>0.01808454738531606</v>
       </c>
       <c r="S242" t="n">
-        <v>0.01105292210108824</v>
+        <v>0.006165236814185178</v>
       </c>
       <c r="T242" t="n">
-        <v>0.02041102369623924</v>
+        <v>0.01809947074470868</v>
       </c>
       <c r="U242" t="n">
-        <v>0.01676082658778257</v>
+        <v>0.002788706251122918</v>
       </c>
       <c r="V242" t="n">
-        <v>0.02046560090863491</v>
+        <v>0.01807830061032771</v>
       </c>
       <c r="W242" t="n">
-        <v>0.007355132343447055</v>
+        <v>0.006909572939162968</v>
       </c>
       <c r="X242" t="n">
-        <v>0.02047773034586647</v>
+        <v>0.01811379984988635</v>
       </c>
       <c r="Y242" t="n">
-        <v>0.01600679321352602</v>
+        <v>0.00906886015836462</v>
       </c>
       <c r="Z242" t="n">
-        <v>0.01801103772292547</v>
+        <v>0.01640752606135195</v>
       </c>
     </row>
     <row r="243">
@@ -23440,76 +23452,76 @@
         <v>0</v>
       </c>
       <c r="C243" t="n">
-        <v>28.36562254539623</v>
+        <v>1.425847408264651</v>
       </c>
       <c r="D243" t="n">
-        <v>14.15048098681374</v>
+        <v>8.383927996208921</v>
       </c>
       <c r="E243" t="n">
-        <v>8.502910834905389</v>
+        <v>1.783148123295697</v>
       </c>
       <c r="F243" t="n">
-        <v>20.95871274141504</v>
+        <v>8.291967342182138</v>
       </c>
       <c r="G243" t="n">
-        <v>17.71882192554118</v>
+        <v>0.9068868761574406</v>
       </c>
       <c r="H243" t="n">
-        <v>25.42198025180063</v>
+        <v>13.47742453157452</v>
       </c>
       <c r="I243" t="n">
-        <v>18.93180334872415</v>
+        <v>1.433498963130106</v>
       </c>
       <c r="J243" t="n">
-        <v>31.13081456262634</v>
+        <v>12.25757779816577</v>
       </c>
       <c r="K243" t="n">
-        <v>17.62224476540855</v>
+        <v>1.360710829023539</v>
       </c>
       <c r="L243" t="n">
-        <v>22.47006245635733</v>
+        <v>10.95070930021865</v>
       </c>
       <c r="M243" t="n">
-        <v>11.89879738574308</v>
+        <v>1.275231382830072</v>
       </c>
       <c r="N243" t="n">
-        <v>27.58720492311125</v>
+        <v>11.85893814132207</v>
       </c>
       <c r="O243" t="n">
-        <v>13.36761929467087</v>
+        <v>1.438742542712019</v>
       </c>
       <c r="P243" t="n">
-        <v>12.17016806345902</v>
+        <v>8.387505321308543</v>
       </c>
       <c r="Q243" t="n">
-        <v>12.96446706321655</v>
+        <v>1.624293152963899</v>
       </c>
       <c r="R243" t="n">
-        <v>20.95871491192886</v>
+        <v>7.861008801631423</v>
       </c>
       <c r="S243" t="n">
-        <v>16.90754655879342</v>
+        <v>1.431502899011766</v>
       </c>
       <c r="T243" t="n">
-        <v>12.01929096956829</v>
+        <v>10.11559433638884</v>
       </c>
       <c r="U243" t="n">
-        <v>16.47547901632764</v>
+        <v>2.259912394458621</v>
       </c>
       <c r="V243" t="n">
-        <v>22.14119763247903</v>
+        <v>9.002035284410331</v>
       </c>
       <c r="W243" t="n">
-        <v>24.24930148734679</v>
+        <v>1.195368580492612</v>
       </c>
       <c r="X243" t="n">
-        <v>16.00095370030918</v>
+        <v>16.18389725384964</v>
       </c>
       <c r="Y243" t="n">
-        <v>18.12268771123986</v>
+        <v>0.8060832327414419</v>
       </c>
       <c r="Z243" t="n">
-        <v>30.26048746588421</v>
+        <v>14.0095550481365</v>
       </c>
     </row>
     <row r="244">
@@ -23522,76 +23534,76 @@
         <v>0</v>
       </c>
       <c r="C244" t="n">
-        <v>0.0004275363302394023</v>
+        <v>0.0003524915173287244</v>
       </c>
       <c r="D244" t="n">
-        <v>0.001079050762384923</v>
+        <v>0.0008079311341168332</v>
       </c>
       <c r="E244" t="n">
-        <v>0.0008916132335963311</v>
+        <v>0.0002503226317789149</v>
       </c>
       <c r="F244" t="n">
-        <v>0.001187569222864009</v>
+        <v>0.0008209331226466808</v>
       </c>
       <c r="G244" t="n">
-        <v>0.0008779565335036311</v>
+        <v>0.0004451519546174183</v>
       </c>
       <c r="H244" t="n">
-        <v>0.00117582371576731</v>
+        <v>0.0008407064672255219</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0007217027675454104</v>
+        <v>0.0002593273049766864</v>
       </c>
       <c r="J244" t="n">
-        <v>0.0009764911189420605</v>
+        <v>0.0007930027867297449</v>
       </c>
       <c r="K244" t="n">
-        <v>0.0004213881621830596</v>
+        <v>0.0003226778562890758</v>
       </c>
       <c r="L244" t="n">
-        <v>0.0007060665430490741</v>
+        <v>0.0008583185217161851</v>
       </c>
       <c r="M244" t="n">
-        <v>0.0009726876777122189</v>
+        <v>0.0003632464719566929</v>
       </c>
       <c r="N244" t="n">
-        <v>0.001257129666697964</v>
+        <v>0.0009038826401045708</v>
       </c>
       <c r="O244" t="n">
-        <v>0.0007448582184657242</v>
+        <v>0.0003472700076026771</v>
       </c>
       <c r="P244" t="n">
-        <v>0.001018938913584775</v>
+        <v>0.0007662473837766236</v>
       </c>
       <c r="Q244" t="n">
-        <v>0.0009727399292511111</v>
+        <v>0.0002917308323441094</v>
       </c>
       <c r="R244" t="n">
-        <v>0.001187569238214033</v>
+        <v>0.0007714085396002405</v>
       </c>
       <c r="S244" t="n">
-        <v>0.0005409772752087537</v>
+        <v>0.0002994833642400094</v>
       </c>
       <c r="T244" t="n">
-        <v>0.001030106825474603</v>
+        <v>0.0008044244966132183</v>
       </c>
       <c r="U244" t="n">
-        <v>0.0008996092708630912</v>
+        <v>0.0001362180481361599</v>
       </c>
       <c r="V244" t="n">
-        <v>0.001164002582498522</v>
+        <v>0.0007566158203758501</v>
       </c>
       <c r="W244" t="n">
-        <v>0.0003579691551681855</v>
+        <v>0.0003374169201988216</v>
       </c>
       <c r="X244" t="n">
-        <v>0.00119433647182922</v>
+        <v>0.0009261893409276804</v>
       </c>
       <c r="Y244" t="n">
-        <v>0.0009566741560622077</v>
+        <v>0.0004499354584246522</v>
       </c>
       <c r="Z244" t="n">
-        <v>0.001059412148959292</v>
+        <v>0.0007529177906128033</v>
       </c>
     </row>
     <row r="245">
@@ -23604,76 +23616,76 @@
         <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>1.026839017149145</v>
+        <v>0.04349357780233074</v>
       </c>
       <c r="D245" t="n">
-        <v>0.4666622241076827</v>
+        <v>0.2341766279192929</v>
       </c>
       <c r="E245" t="n">
-        <v>0.2613393817718332</v>
+        <v>0.05378700688401011</v>
       </c>
       <c r="F245" t="n">
-        <v>0.7750933629076193</v>
+        <v>0.2352322505883509</v>
       </c>
       <c r="G245" t="n">
-        <v>0.6142103415771215</v>
+        <v>0.02794108658853721</v>
       </c>
       <c r="H245" t="n">
-        <v>0.9107123442350574</v>
+        <v>0.3915463225496937</v>
       </c>
       <c r="I245" t="n">
-        <v>0.605994668744872</v>
+        <v>0.04347087950214247</v>
       </c>
       <c r="J245" t="n">
-        <v>1.141072594107498</v>
+        <v>0.3361473739869703</v>
       </c>
       <c r="K245" t="n">
-        <v>0.5199159645800918</v>
+        <v>0.04147437345139635</v>
       </c>
       <c r="L245" t="n">
-        <v>0.7274695781481741</v>
+        <v>0.32431049116598</v>
       </c>
       <c r="M245" t="n">
-        <v>0.397737887121254</v>
+        <v>0.03901673576111927</v>
       </c>
       <c r="N245" t="n">
-        <v>1.056945097609491</v>
+        <v>0.3692386796416888</v>
       </c>
       <c r="O245" t="n">
-        <v>0.4289643866992537</v>
+        <v>0.04386589094217083</v>
       </c>
       <c r="P245" t="n">
-        <v>0.3797047119715596</v>
+        <v>0.2289054837956063</v>
       </c>
       <c r="Q245" t="n">
-        <v>0.4333647393375555</v>
+        <v>0.04923072172733895</v>
       </c>
       <c r="R245" t="n">
-        <v>0.7750934489218022</v>
+        <v>0.2099445002409166</v>
       </c>
       <c r="S245" t="n">
-        <v>0.5169570904128881</v>
+        <v>0.04352118372271088</v>
       </c>
       <c r="T245" t="n">
-        <v>0.3789996501097935</v>
+        <v>0.2813019972849387</v>
       </c>
       <c r="U245" t="n">
-        <v>0.5519191430477911</v>
+        <v>0.06898087645763562</v>
       </c>
       <c r="V245" t="n">
-        <v>0.7853647821958591</v>
+        <v>0.2358988341575143</v>
       </c>
       <c r="W245" t="n">
-        <v>0.737189445615523</v>
+        <v>0.03655866109148044</v>
       </c>
       <c r="X245" t="n">
-        <v>0.5819198452093163</v>
+        <v>0.5168049842088583</v>
       </c>
       <c r="Y245" t="n">
-        <v>0.6750367181761315</v>
+        <v>0.0251091309444606</v>
       </c>
       <c r="Z245" t="n">
-        <v>1.10937952509565</v>
+        <v>0.4019899521055668</v>
       </c>
     </row>
     <row r="246">
@@ -23686,76 +23698,76 @@
         <v>0</v>
       </c>
       <c r="C246" t="n">
-        <v>0.01078514179090866</v>
+        <v>0.01064080721232257</v>
       </c>
       <c r="D246" t="n">
-        <v>0.02999733554308342</v>
+        <v>0.02666658996209572</v>
       </c>
       <c r="E246" t="n">
-        <v>0.02666666662729215</v>
+        <v>0.007636002687194838</v>
       </c>
       <c r="F246" t="n">
-        <v>0.02931116281937293</v>
+        <v>0.02666660877624395</v>
       </c>
       <c r="G246" t="n">
-        <v>0.02317309769072732</v>
+        <v>0.0133332640541636</v>
       </c>
       <c r="H246" t="n">
-        <v>0.02999319827031129</v>
+        <v>0.02663652636272205</v>
       </c>
       <c r="I246" t="n">
-        <v>0.02068402159207633</v>
+        <v>0.007870661197657147</v>
       </c>
       <c r="J246" t="n">
-        <v>0.02432002610198897</v>
+        <v>0.02666342426034089</v>
       </c>
       <c r="K246" t="n">
-        <v>0.01313513387617791</v>
+        <v>0.009747633842985546</v>
       </c>
       <c r="L246" t="n">
-        <v>0.01999835003604119</v>
+        <v>0.02666586168742614</v>
       </c>
       <c r="M246" t="n">
-        <v>0.02666666665907403</v>
+        <v>0.01093558373354588</v>
       </c>
       <c r="N246" t="n">
-        <v>0.02990550947903199</v>
+        <v>0.02666663929274192</v>
       </c>
       <c r="O246" t="n">
-        <v>0.02129602835720108</v>
+        <v>0.01048774505352269</v>
       </c>
       <c r="P246" t="n">
-        <v>0.02999992199315222</v>
+        <v>0.02590041207908692</v>
       </c>
       <c r="Q246" t="n">
-        <v>0.02666608755817053</v>
+        <v>0.00885882785731207</v>
       </c>
       <c r="R246" t="n">
-        <v>0.02931116297127061</v>
+        <v>0.02666397595421394</v>
       </c>
       <c r="S246" t="n">
-        <v>0.01625479678650711</v>
+        <v>0.009068165202733762</v>
       </c>
       <c r="T246" t="n">
-        <v>0.02999847144907409</v>
+        <v>0.02666655141909509</v>
       </c>
       <c r="U246" t="n">
-        <v>0.02460147431915601</v>
+        <v>0.004101328547802681</v>
       </c>
       <c r="V246" t="n">
-        <v>0.02999999981345326</v>
+        <v>0.02666348142326606</v>
       </c>
       <c r="W246" t="n">
-        <v>0.01081791702206967</v>
+        <v>0.01016190925662516</v>
       </c>
       <c r="X246" t="n">
-        <v>0.02999999363570218</v>
+        <v>0.02661498617027291</v>
       </c>
       <c r="Y246" t="n">
-        <v>0.02343618532665171</v>
+        <v>0.01333332896249214</v>
       </c>
       <c r="Z246" t="n">
-        <v>0.02638090929501263</v>
+        <v>0.02415953841766024</v>
       </c>
     </row>
     <row r="247">
@@ -23768,76 +23780,76 @@
         <v>0</v>
       </c>
       <c r="C247" t="n">
-        <v>27.34237857551073</v>
+        <v>1.385900766199761</v>
       </c>
       <c r="D247" t="n">
-        <v>13.69381787455375</v>
+        <v>8.158640231610326</v>
       </c>
       <c r="E247" t="n">
-        <v>8.250460342009321</v>
+        <v>1.731906450640752</v>
       </c>
       <c r="F247" t="n">
-        <v>20.19338976611387</v>
+        <v>8.065623961185869</v>
       </c>
       <c r="G247" t="n">
-        <v>17.11233594986097</v>
+        <v>0.8833902109202912</v>
       </c>
       <c r="H247" t="n">
-        <v>24.52126564032234</v>
+        <v>13.09475705114573</v>
       </c>
       <c r="I247" t="n">
-        <v>18.3327033538433</v>
+        <v>1.392651637360516</v>
       </c>
       <c r="J247" t="n">
-        <v>29.99784864388617</v>
+        <v>11.93031823226558</v>
       </c>
       <c r="K247" t="n">
-        <v>17.10670717878718</v>
+        <v>1.322485666853138</v>
       </c>
       <c r="L247" t="n">
-        <v>21.74925899488784</v>
+        <v>10.63528742961514</v>
       </c>
       <c r="M247" t="n">
-        <v>11.50994838750819</v>
+        <v>1.239859841646801</v>
       </c>
       <c r="N247" t="n">
-        <v>26.54022832866143</v>
+        <v>11.49858834144462</v>
       </c>
       <c r="O247" t="n">
-        <v>12.94575358409068</v>
+        <v>1.398372566787689</v>
       </c>
       <c r="P247" t="n">
-        <v>11.80046332548518</v>
+        <v>8.167233308205965</v>
       </c>
       <c r="Q247" t="n">
-        <v>12.53999101973171</v>
+        <v>1.578015373855664</v>
       </c>
       <c r="R247" t="n">
-        <v>20.19339185066415</v>
+        <v>7.659952293375245</v>
       </c>
       <c r="S247" t="n">
-        <v>16.39600773397603</v>
+        <v>1.391004437023299</v>
       </c>
       <c r="T247" t="n">
-        <v>11.65029080994153</v>
+        <v>9.843181189576937</v>
       </c>
       <c r="U247" t="n">
-        <v>15.93176036471957</v>
+        <v>2.192298627516919</v>
       </c>
       <c r="V247" t="n">
-        <v>21.36583285022099</v>
+        <v>8.775024277393905</v>
       </c>
       <c r="W247" t="n">
-        <v>23.51571801407196</v>
+        <v>1.162197222486674</v>
       </c>
       <c r="X247" t="n">
-        <v>15.42903385297843</v>
+        <v>15.67596393169754</v>
       </c>
       <c r="Y247" t="n">
-        <v>17.45546305483927</v>
+        <v>0.7854185447844786</v>
       </c>
       <c r="Z247" t="n">
-        <v>29.15990157722024</v>
+        <v>13.61561827550349</v>
       </c>
     </row>
     <row r="248">
@@ -23850,76 +23862,76 @@
         <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>565.1450530074314</v>
+        <v>211.138208031226</v>
       </c>
       <c r="D248" t="n">
-        <v>605.8192429986784</v>
+        <v>492.7554474967418</v>
       </c>
       <c r="E248" t="n">
-        <v>481.1175318271201</v>
+        <v>205.5338115043497</v>
       </c>
       <c r="F248" t="n">
-        <v>594.8603971508435</v>
+        <v>475.4211971086032</v>
       </c>
       <c r="G248" t="n">
-        <v>453.8802419654093</v>
+        <v>200.8617598355465</v>
       </c>
       <c r="H248" t="n">
-        <v>538.9319256665227</v>
+        <v>434.0297979938829</v>
       </c>
       <c r="I248" t="n">
-        <v>420.1653702806221</v>
+        <v>194.0749848970596</v>
       </c>
       <c r="J248" t="n">
-        <v>524.543252656714</v>
+        <v>416.2394307823951</v>
       </c>
       <c r="K248" t="n">
-        <v>467.4165205600802</v>
+        <v>204.4283219128965</v>
       </c>
       <c r="L248" t="n">
-        <v>563.4842488071172</v>
+        <v>458.711165971249</v>
       </c>
       <c r="M248" t="n">
-        <v>451.6038378106572</v>
+        <v>197.2669891444859</v>
       </c>
       <c r="N248" t="n">
-        <v>555.8306662222466</v>
+        <v>441.4529768317523</v>
       </c>
       <c r="O248" t="n">
-        <v>498.5380986479729</v>
+        <v>211.183586767671</v>
       </c>
       <c r="P248" t="n">
-        <v>599.555498346737</v>
+        <v>492.4693746810674</v>
       </c>
       <c r="Q248" t="n">
-        <v>473.6750329373967</v>
+        <v>205.1036073026733</v>
       </c>
       <c r="R248" t="n">
-        <v>594.8937202052857</v>
+        <v>474.7746573704857</v>
       </c>
       <c r="S248" t="n">
-        <v>491.4960313167109</v>
+        <v>214.7825719055457</v>
       </c>
       <c r="T248" t="n">
-        <v>607.8913495993135</v>
+        <v>482.8897129093636</v>
       </c>
       <c r="U248" t="n">
-        <v>466.0783463575596</v>
+        <v>211.9890699767341</v>
       </c>
       <c r="V248" t="n">
-        <v>567.1018378100835</v>
+        <v>467.1502952611737</v>
       </c>
       <c r="W248" t="n">
-        <v>576.9013081900902</v>
+        <v>247.7916221957092</v>
       </c>
       <c r="X248" t="n">
-        <v>743.374054193562</v>
+        <v>547.5406650585937</v>
       </c>
       <c r="Y248" t="n">
-        <v>572.832656799097</v>
+        <v>241.7553128571813</v>
       </c>
       <c r="Z248" t="n">
-        <v>667.8382074750065</v>
+        <v>530.4252619472896</v>
       </c>
     </row>
     <row r="249">
@@ -23932,76 +23944,76 @@
         <v>0</v>
       </c>
       <c r="C249" t="n">
-        <v>10.45908421679052</v>
+        <v>4.038970133853767</v>
       </c>
       <c r="D249" t="n">
-        <v>11.26698738331131</v>
+        <v>9.252590791612363</v>
       </c>
       <c r="E249" t="n">
-        <v>9.058625530452</v>
+        <v>3.945563525072495</v>
       </c>
       <c r="F249" t="n">
-        <v>11.08433995251406</v>
+        <v>8.96368661847672</v>
       </c>
       <c r="G249" t="n">
-        <v>8.604670699423487</v>
+        <v>3.867695997259109</v>
       </c>
       <c r="H249" t="n">
-        <v>10.15219876110871</v>
+        <v>8.273829966564714</v>
       </c>
       <c r="I249" t="n">
-        <v>8.042756171343701</v>
+        <v>3.754583081617659</v>
       </c>
       <c r="J249" t="n">
-        <v>9.912387544278564</v>
+        <v>7.977323846373251</v>
       </c>
       <c r="K249" t="n">
-        <v>8.830275342668001</v>
+        <v>3.927138698548275</v>
       </c>
       <c r="L249" t="n">
-        <v>10.56140414678529</v>
+        <v>8.685186099520816</v>
       </c>
       <c r="M249" t="n">
-        <v>8.56673063017762</v>
+        <v>3.807783152408097</v>
       </c>
       <c r="N249" t="n">
-        <v>10.43384443703744</v>
+        <v>8.397549613862536</v>
       </c>
       <c r="O249" t="n">
-        <v>9.348968310799547</v>
+        <v>4.039726446127849</v>
       </c>
       <c r="P249" t="n">
-        <v>11.16259163911228</v>
+        <v>9.247822911351124</v>
       </c>
       <c r="Q249" t="n">
-        <v>8.934583882289944</v>
+        <v>3.938393455044554</v>
       </c>
       <c r="R249" t="n">
-        <v>11.08489533675476</v>
+        <v>8.95291095617476</v>
       </c>
       <c r="S249" t="n">
-        <v>9.231600521945181</v>
+        <v>4.099709531759094</v>
       </c>
       <c r="T249" t="n">
-        <v>11.30152249332189</v>
+        <v>9.088161881822725</v>
       </c>
       <c r="U249" t="n">
-        <v>8.807972439292659</v>
+        <v>4.053151166278901</v>
       </c>
       <c r="V249" t="n">
-        <v>10.62169729683472</v>
+        <v>8.825838254352893</v>
       </c>
       <c r="W249" t="n">
-        <v>10.65502180316817</v>
+        <v>4.649860369928486</v>
       </c>
       <c r="X249" t="n">
-        <v>13.5595675698927</v>
+        <v>10.16567775097656</v>
       </c>
       <c r="Y249" t="n">
-        <v>10.58721094665162</v>
+        <v>4.549255214286354</v>
       </c>
       <c r="Z249" t="n">
-        <v>12.3006367912501</v>
+        <v>9.880421032454827</v>
       </c>
     </row>
     <row r="250">
@@ -24014,76 +24026,76 @@
         <v>0</v>
       </c>
       <c r="C250" t="n">
-        <v>3.057244748858213</v>
+        <v>3.579351448906465</v>
       </c>
       <c r="D250" t="n">
-        <v>2.288515553800382</v>
+        <v>2.471992607665821</v>
       </c>
       <c r="E250" t="n">
-        <v>2.534016580734052</v>
+        <v>3.964832229173919</v>
       </c>
       <c r="F250" t="n">
-        <v>2.255222894529999</v>
+        <v>2.492384299637393</v>
       </c>
       <c r="G250" t="n">
-        <v>2.623653242389263</v>
+        <v>3.449096220250571</v>
       </c>
       <c r="H250" t="n">
-        <v>2.382859337400631</v>
+        <v>2.57188995485036</v>
       </c>
       <c r="I250" t="n">
-        <v>2.764452211713482</v>
+        <v>4.0284975730433</v>
       </c>
       <c r="J250" t="n">
-        <v>2.512004167546767</v>
+        <v>2.589106335077204</v>
       </c>
       <c r="K250" t="n">
-        <v>3.066812936602169</v>
+        <v>3.718431865315635</v>
       </c>
       <c r="L250" t="n">
-        <v>2.602358807926371</v>
+        <v>2.543966929046572</v>
       </c>
       <c r="M250" t="n">
-        <v>2.52573402649594</v>
+        <v>3.611206784696086</v>
       </c>
       <c r="N250" t="n">
-        <v>2.293272756548705</v>
+        <v>2.556123733655526</v>
       </c>
       <c r="O250" t="n">
-        <v>2.592080398895427</v>
+        <v>3.596153267578491</v>
       </c>
       <c r="P250" t="n">
-        <v>2.305975426688285</v>
+        <v>2.484216954909444</v>
       </c>
       <c r="Q250" t="n">
-        <v>2.437655251697213</v>
+        <v>3.794852512846917</v>
       </c>
       <c r="R250" t="n">
-        <v>2.255222899480308</v>
+        <v>2.484514784470691</v>
       </c>
       <c r="S250" t="n">
-        <v>2.882539265643225</v>
+        <v>3.792554747325702</v>
       </c>
       <c r="T250" t="n">
-        <v>2.442349011150433</v>
+        <v>2.536776448974847</v>
       </c>
       <c r="U250" t="n">
-        <v>2.562214965608081</v>
+        <v>4.803240829853182</v>
       </c>
       <c r="V250" t="n">
-        <v>2.316441675087255</v>
+        <v>2.561291546921503</v>
       </c>
       <c r="W250" t="n">
-        <v>3.314673657382929</v>
+        <v>3.716007175070244</v>
       </c>
       <c r="X250" t="n">
-        <v>2.295719152024307</v>
+        <v>2.565058986762587</v>
       </c>
       <c r="Y250" t="n">
-        <v>2.583407686299188</v>
+        <v>3.507615070234511</v>
       </c>
       <c r="Z250" t="n">
-        <v>2.446694796265906</v>
+        <v>2.657314720144654</v>
       </c>
     </row>
   </sheetData>
